--- a/maliyet_2024_test.xlsx
+++ b/maliyet_2024_test.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.##"/>
     <numFmt numFmtId="166" formatCode="#,##0.0000 &quot;₺&quot;"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +52,14 @@
       <color rgb="001B5E20"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001A237E"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -85,6 +91,11 @@
         <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C5CAE9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -112,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -151,6 +162,21 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -518,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L255"/>
+  <dimension ref="A1:L271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -538,7 +564,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CEO ERP — Maliyet Raporu  |  Yöntem: Ağırlıklı Ortalama  |  Dönem: 01.01.2024 – 31.12.2024  |  Oluşturma: 04.06.2026 11:17</t>
+          <t>CEO ERP — Maliyet Raporu  |  Yöntem: Ağırlıklı Ortalama  |  Dönem: 01.01.2024 – 31.12.2024  |  Oluşturma: 04.06.2026 11:42</t>
         </is>
       </c>
     </row>
@@ -1917,48 +1943,48 @@
       <c r="L41" s="6" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>ALT-MAMÜL</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
         <is>
           <t>GMP-101-230107</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C42" s="15" t="inlineStr">
         <is>
           <t>PORTATİF IŞIK KAYNAĞI V05</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" s="14" t="inlineStr">
         <is>
           <t>YMB-V00R00-220007</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E42" s="15" t="inlineStr">
         <is>
           <t>LED BÜTÜNÜ</t>
         </is>
       </c>
-      <c r="F42" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H42" s="9" t="n">
+      <c r="F42" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H42" s="17" t="n">
         <v>199.74</v>
       </c>
-      <c r="I42" s="10" t="n">
+      <c r="I42" s="18" t="n">
         <v>199.74</v>
       </c>
-      <c r="J42" s="6" t="n"/>
-      <c r="K42" s="6" t="n"/>
-      <c r="L42" s="6" t="n"/>
+      <c r="J42" s="14" t="n"/>
+      <c r="K42" s="14" t="n"/>
+      <c r="L42" s="14" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
@@ -1978,12 +2004,13 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>YMB-V00R00-220008</t>
+          <t>GMP-300-230004</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>SOĞUTUCU GÖVDE BÜTÜNÜ</t>
+          <t xml:space="preserve">    PORTATİF DİZGİ POKO PİN KART (Seri Üretim) 
+</t>
         </is>
       </c>
       <c r="F43" s="8" t="n">
@@ -1995,10 +2022,10 @@
         </is>
       </c>
       <c r="H43" s="9" t="n">
-        <v>1498.3051</v>
+        <v>199.74</v>
       </c>
       <c r="I43" s="10" t="n">
-        <v>1498.31</v>
+        <v>199.74</v>
       </c>
       <c r="J43" s="6" t="n"/>
       <c r="K43" s="6" t="n"/>
@@ -2022,12 +2049,13 @@
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>YMB-V00R00-220009</t>
+          <t>GMP-300-230005</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>BUTON BÜTÜNÜ</t>
+          <t xml:space="preserve">    PORTATİF DİZGİ LED KART (SERİ ÜRETİM)
+</t>
         </is>
       </c>
       <c r="F44" s="8" t="n">
@@ -2039,10 +2067,10 @@
         </is>
       </c>
       <c r="H44" s="9" t="n">
-        <v>602.6314</v>
+        <v>0</v>
       </c>
       <c r="I44" s="10" t="n">
-        <v>602.63</v>
+        <v>0</v>
       </c>
       <c r="J44" s="6" t="n"/>
       <c r="K44" s="6" t="n"/>
@@ -2066,12 +2094,12 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>YMB-V00R00-220010</t>
+          <t>YMB-V00R00-220008</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>EKRAN BÜTÜNÜ</t>
+          <t>SOĞUTUCU GÖVDE BÜTÜNÜ</t>
         </is>
       </c>
       <c r="F45" s="8" t="n">
@@ -2083,10 +2111,10 @@
         </is>
       </c>
       <c r="H45" s="9" t="n">
-        <v>198.7322</v>
+        <v>1498.3051</v>
       </c>
       <c r="I45" s="10" t="n">
-        <v>198.73</v>
+        <v>1498.31</v>
       </c>
       <c r="J45" s="6" t="n"/>
       <c r="K45" s="6" t="n"/>
@@ -2110,12 +2138,12 @@
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>YMB-V00R00-220011</t>
+          <t>YMB-V00R00-220009</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>ANA GÖVDE BÜTÜNÜ</t>
+          <t>BUTON BÜTÜNÜ</t>
         </is>
       </c>
       <c r="F46" s="8" t="n">
@@ -2127,276 +2155,276 @@
         </is>
       </c>
       <c r="H46" s="9" t="n">
-        <v>4197.0961</v>
+        <v>602.6314</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>4197.1</v>
+        <v>602.63</v>
       </c>
       <c r="J46" s="6" t="n"/>
       <c r="K46" s="6" t="n"/>
       <c r="L46" s="6" t="n"/>
     </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="11" t="inlineStr">
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>GMP-101-230107</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>PORTATİF IŞIK KAYNAĞI V05</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>YMB-V00R00-220010</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>EKRAN BÜTÜNÜ</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H47" s="9" t="n">
+        <v>198.7322</v>
+      </c>
+      <c r="I47" s="10" t="n">
+        <v>198.73</v>
+      </c>
+      <c r="J47" s="6" t="n"/>
+      <c r="K47" s="6" t="n"/>
+      <c r="L47" s="6" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>GMP-101-230107</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>PORTATİF IŞIK KAYNAĞI V05</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>YMB-V00R00-220011</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>ANA GÖVDE BÜTÜNÜ</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="n">
+        <v>4197.0961</v>
+      </c>
+      <c r="I48" s="10" t="n">
+        <v>4197.1</v>
+      </c>
+      <c r="J48" s="6" t="n"/>
+      <c r="K48" s="6" t="n"/>
+      <c r="L48" s="6" t="n"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B47" s="11" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>GMP-101-230107</t>
         </is>
       </c>
-      <c r="C47" s="12" t="inlineStr">
+      <c r="C49" s="12" t="inlineStr">
         <is>
           <t>PORTATİF IŞIK KAYNAĞI V05</t>
         </is>
       </c>
-      <c r="D47" s="11" t="n"/>
-      <c r="E47" s="11" t="n"/>
-      <c r="F47" s="11" t="n"/>
-      <c r="G47" s="11" t="n"/>
-      <c r="H47" s="11" t="n"/>
-      <c r="I47" s="11" t="n"/>
-      <c r="J47" s="13" t="n">
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="11" t="n"/>
+      <c r="F49" s="11" t="n"/>
+      <c r="G49" s="11" t="n"/>
+      <c r="H49" s="11" t="n"/>
+      <c r="I49" s="11" t="n"/>
+      <c r="J49" s="13" t="n">
         <v>10096.09</v>
       </c>
-      <c r="K47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="13" t="n">
+      <c r="K49" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="13" t="n">
         <v>10096.09</v>
       </c>
     </row>
-    <row r="48" ht="6" customHeight="1"/>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+    <row r="50" ht="6" customHeight="1"/>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>GMP-200-2230286</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>LÜP GÖVDE</t>
         </is>
       </c>
-      <c r="D49" s="3" t="n"/>
-      <c r="E49" s="3" t="n"/>
-      <c r="F49" s="3" t="n"/>
-      <c r="G49" s="3" t="n"/>
-      <c r="H49" s="3" t="n"/>
-      <c r="I49" s="3" t="n"/>
-      <c r="J49" s="5" t="n">
+      <c r="D51" s="3" t="n"/>
+      <c r="E51" s="3" t="n"/>
+      <c r="F51" s="3" t="n"/>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+      <c r="I51" s="3" t="n"/>
+      <c r="J51" s="5" t="n">
         <v>639</v>
       </c>
-      <c r="K49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="5" t="n">
+      <c r="K51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="5" t="n">
         <v>639</v>
       </c>
     </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>GMP-200-2230286</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>LÜP GÖVDE</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>GMP-200-230286</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>LÜP GÖVDE</t>
         </is>
       </c>
-      <c r="F50" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H50" s="9" t="n">
+      <c r="F52" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H52" s="9" t="n">
         <v>639</v>
       </c>
-      <c r="I50" s="10" t="n">
+      <c r="I52" s="10" t="n">
         <v>639</v>
       </c>
-      <c r="J50" s="6" t="n"/>
-      <c r="K50" s="6" t="n"/>
-      <c r="L50" s="6" t="n"/>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="11" t="inlineStr">
+      <c r="J52" s="6" t="n"/>
+      <c r="K52" s="6" t="n"/>
+      <c r="L52" s="6" t="n"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>GMP-200-2230286</t>
         </is>
       </c>
-      <c r="C51" s="12" t="inlineStr">
+      <c r="C53" s="12" t="inlineStr">
         <is>
           <t>LÜP GÖVDE</t>
         </is>
       </c>
-      <c r="D51" s="11" t="n"/>
-      <c r="E51" s="11" t="n"/>
-      <c r="F51" s="11" t="n"/>
-      <c r="G51" s="11" t="n"/>
-      <c r="H51" s="11" t="n"/>
-      <c r="I51" s="11" t="n"/>
-      <c r="J51" s="13" t="n">
+      <c r="D53" s="11" t="n"/>
+      <c r="E53" s="11" t="n"/>
+      <c r="F53" s="11" t="n"/>
+      <c r="G53" s="11" t="n"/>
+      <c r="H53" s="11" t="n"/>
+      <c r="I53" s="11" t="n"/>
+      <c r="J53" s="13" t="n">
         <v>639</v>
       </c>
-      <c r="K51" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="13" t="n">
+      <c r="K53" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="13" t="n">
         <v>639</v>
       </c>
     </row>
-    <row r="52" ht="6" customHeight="1"/>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
+    <row r="54" ht="6" customHeight="1"/>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>GMP-200-230044</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>120-122 MM NAMLU ADAPTÖRÜ (V-SP)</t>
         </is>
       </c>
-      <c r="D53" s="3" t="n"/>
-      <c r="E53" s="3" t="n"/>
-      <c r="F53" s="3" t="n"/>
-      <c r="G53" s="3" t="n"/>
-      <c r="H53" s="3" t="n"/>
-      <c r="I53" s="3" t="n"/>
-      <c r="J53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>GMP-200-230044</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="inlineStr">
-        <is>
-          <t>120-122 MM NAMLU ADAPTÖRÜ (V-SP)</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>GMP-101-230044</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>120 - 122 MM NAMLU ADAPTÖRÜ (V-SP)</t>
-        </is>
-      </c>
-      <c r="F54" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="6" t="n"/>
-      <c r="K54" s="6" t="n"/>
-      <c r="L54" s="6" t="n"/>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>GMP-200-230044</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>120-122 MM NAMLU ADAPTÖRÜ (V-SP)</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>GMP-200-240239</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40 X 50 BORU </t>
-        </is>
-      </c>
-      <c r="F55" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="6" t="n"/>
-      <c r="K55" s="6" t="n"/>
-      <c r="L55" s="6" t="n"/>
+      <c r="D55" s="3" t="n"/>
+      <c r="E55" s="3" t="n"/>
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+      <c r="I55" s="3" t="n"/>
+      <c r="J55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
@@ -2416,12 +2444,12 @@
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>GMP-200-240244</t>
+          <t>GMP-101-230044</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">GÖBEK KAM 3 </t>
+          <t>120 - 122 MM NAMLU ADAPTÖRÜ (V-SP)</t>
         </is>
       </c>
       <c r="F56" s="8" t="n">
@@ -2460,12 +2488,12 @@
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>GMP-200-240248</t>
+          <t>GMP-200-240239</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>120 MM ÇENE</t>
+          <t xml:space="preserve">40 X 50 BORU </t>
         </is>
       </c>
       <c r="F57" s="8" t="n">
@@ -2504,12 +2532,12 @@
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>GMP-200-240249</t>
+          <t>GMP-200-240244</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>120 MM ÖN FLANŞIL</t>
+          <t xml:space="preserve">GÖBEK KAM 3 </t>
         </is>
       </c>
       <c r="F58" s="8" t="n">
@@ -2548,12 +2576,12 @@
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>GMP-200-240251</t>
+          <t>GMP-200-240248</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">YAY KAPAK </t>
+          <t>120 MM ÇENE</t>
         </is>
       </c>
       <c r="F59" s="8" t="n">
@@ -2592,12 +2620,12 @@
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>GMP-200-240252</t>
+          <t>GMP-200-240249</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>120 MM YATAK</t>
+          <t>120 MM ÖN FLANŞIL</t>
         </is>
       </c>
       <c r="F60" s="8" t="n">
@@ -2636,13 +2664,12 @@
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>GMP-200-240255</t>
+          <t>GMP-200-240251</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">120-10mm PİM
-</t>
+          <t xml:space="preserve">YAY KAPAK </t>
         </is>
       </c>
       <c r="F61" s="8" t="n">
@@ -2663,3558 +2690,3627 @@
       <c r="K61" s="6" t="n"/>
       <c r="L61" s="6" t="n"/>
     </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="11" t="inlineStr">
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>GMP-200-230044</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>120-122 MM NAMLU ADAPTÖRÜ (V-SP)</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>GMP-200-240252</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>120 MM YATAK</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="6" t="n"/>
+      <c r="K62" s="6" t="n"/>
+      <c r="L62" s="6" t="n"/>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>GMP-200-230044</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>120-122 MM NAMLU ADAPTÖRÜ (V-SP)</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>GMP-200-240255</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120-10mm PİM
+</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="6" t="n"/>
+      <c r="K63" s="6" t="n"/>
+      <c r="L63" s="6" t="n"/>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B62" s="11" t="inlineStr">
+      <c r="B64" s="11" t="inlineStr">
         <is>
           <t>GMP-200-230044</t>
         </is>
       </c>
-      <c r="C62" s="12" t="inlineStr">
+      <c r="C64" s="12" t="inlineStr">
         <is>
           <t>120-122 MM NAMLU ADAPTÖRÜ (V-SP)</t>
         </is>
       </c>
-      <c r="D62" s="11" t="n"/>
-      <c r="E62" s="11" t="n"/>
-      <c r="F62" s="11" t="n"/>
-      <c r="G62" s="11" t="n"/>
-      <c r="H62" s="11" t="n"/>
-      <c r="I62" s="11" t="n"/>
-      <c r="J62" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" ht="6" customHeight="1"/>
-    <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="D64" s="11" t="n"/>
+      <c r="E64" s="11" t="n"/>
+      <c r="F64" s="11" t="n"/>
+      <c r="G64" s="11" t="n"/>
+      <c r="H64" s="11" t="n"/>
+      <c r="I64" s="11" t="n"/>
+      <c r="J64" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" ht="6" customHeight="1"/>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>GMP-200-230290.</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>LÜP TABAN CAM ÇERÇEVESİ</t>
         </is>
       </c>
-      <c r="D64" s="3" t="n"/>
-      <c r="E64" s="3" t="n"/>
-      <c r="F64" s="3" t="n"/>
-      <c r="G64" s="3" t="n"/>
-      <c r="H64" s="3" t="n"/>
-      <c r="I64" s="3" t="n"/>
-      <c r="J64" s="5" t="n">
+      <c r="D66" s="3" t="n"/>
+      <c r="E66" s="3" t="n"/>
+      <c r="F66" s="3" t="n"/>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+      <c r="I66" s="3" t="n"/>
+      <c r="J66" s="5" t="n">
         <v>229.55</v>
       </c>
-      <c r="K64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="5" t="n">
+      <c r="K66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="5" t="n">
         <v>229.55</v>
       </c>
     </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>GMP-200-230290.</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>LÜP TABAN CAM ÇERÇEVESİ</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t>GMP-200-230290</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>LÜP TABAN CAM ÇERÇEVESİ</t>
         </is>
       </c>
-      <c r="F65" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H65" s="9" t="n">
+      <c r="F67" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H67" s="9" t="n">
         <v>229.55</v>
       </c>
-      <c r="I65" s="10" t="n">
+      <c r="I67" s="10" t="n">
         <v>229.55</v>
       </c>
-      <c r="J65" s="6" t="n"/>
-      <c r="K65" s="6" t="n"/>
-      <c r="L65" s="6" t="n"/>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
+      <c r="J67" s="6" t="n"/>
+      <c r="K67" s="6" t="n"/>
+      <c r="L67" s="6" t="n"/>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B66" s="11" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>GMP-200-230290.</t>
         </is>
       </c>
-      <c r="C66" s="12" t="inlineStr">
+      <c r="C68" s="12" t="inlineStr">
         <is>
           <t>LÜP TABAN CAM ÇERÇEVESİ</t>
         </is>
       </c>
-      <c r="D66" s="11" t="n"/>
-      <c r="E66" s="11" t="n"/>
-      <c r="F66" s="11" t="n"/>
-      <c r="G66" s="11" t="n"/>
-      <c r="H66" s="11" t="n"/>
-      <c r="I66" s="11" t="n"/>
-      <c r="J66" s="13" t="n">
+      <c r="D68" s="11" t="n"/>
+      <c r="E68" s="11" t="n"/>
+      <c r="F68" s="11" t="n"/>
+      <c r="G68" s="11" t="n"/>
+      <c r="H68" s="11" t="n"/>
+      <c r="I68" s="11" t="n"/>
+      <c r="J68" s="13" t="n">
         <v>229.55</v>
       </c>
-      <c r="K66" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="13" t="n">
+      <c r="K68" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="13" t="n">
         <v>229.55</v>
       </c>
     </row>
-    <row r="67" ht="6" customHeight="1"/>
-    <row r="68" ht="22" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
+    <row r="69" ht="6" customHeight="1"/>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>GMP-200-230558</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">8,59 MM NAMLU ADAPTÖRÜ (V-SP) </t>
         </is>
       </c>
-      <c r="D68" s="3" t="n"/>
-      <c r="E68" s="3" t="n"/>
-      <c r="F68" s="3" t="n"/>
-      <c r="G68" s="3" t="n"/>
-      <c r="H68" s="3" t="n"/>
-      <c r="I68" s="3" t="n"/>
-      <c r="J68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
+      <c r="D70" s="3" t="n"/>
+      <c r="E70" s="3" t="n"/>
+      <c r="F70" s="3" t="n"/>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+      <c r="I70" s="3" t="n"/>
+      <c r="J70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>GMP-200-230558</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">8,59 MM NAMLU ADAPTÖRÜ (V-SP) </t>
         </is>
       </c>
-      <c r="D69" s="6" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr">
         <is>
           <t>GMP-101-230034</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="E71" s="7" t="inlineStr">
         <is>
           <t>8,59 MM NAMLU ADAPTÖRÜ (V-SP)</t>
         </is>
       </c>
-      <c r="F69" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="6" t="n"/>
-      <c r="K69" s="6" t="n"/>
-      <c r="L69" s="6" t="n"/>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="11" t="inlineStr">
+      <c r="F71" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H71" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="6" t="n"/>
+      <c r="K71" s="6" t="n"/>
+      <c r="L71" s="6" t="n"/>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B70" s="11" t="inlineStr">
+      <c r="B72" s="11" t="inlineStr">
         <is>
           <t>GMP-200-230558</t>
         </is>
       </c>
-      <c r="C70" s="12" t="inlineStr">
+      <c r="C72" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">8,59 MM NAMLU ADAPTÖRÜ (V-SP) </t>
         </is>
       </c>
-      <c r="D70" s="11" t="n"/>
-      <c r="E70" s="11" t="n"/>
-      <c r="F70" s="11" t="n"/>
-      <c r="G70" s="11" t="n"/>
-      <c r="H70" s="11" t="n"/>
-      <c r="I70" s="11" t="n"/>
-      <c r="J70" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" ht="6" customHeight="1"/>
-    <row r="72" ht="22" customHeight="1">
-      <c r="A72" s="3" t="inlineStr">
+      <c r="D72" s="11" t="n"/>
+      <c r="E72" s="11" t="n"/>
+      <c r="F72" s="11" t="n"/>
+      <c r="G72" s="11" t="n"/>
+      <c r="H72" s="11" t="n"/>
+      <c r="I72" s="11" t="n"/>
+      <c r="J72" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" ht="6" customHeight="1"/>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>GMP-200-230560</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">20 MM NAMLU ADAPTÖRÜ (V-SP) </t>
         </is>
       </c>
-      <c r="D72" s="3" t="n"/>
-      <c r="E72" s="3" t="n"/>
-      <c r="F72" s="3" t="n"/>
-      <c r="G72" s="3" t="n"/>
-      <c r="H72" s="3" t="n"/>
-      <c r="I72" s="3" t="n"/>
-      <c r="J72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="D74" s="3" t="n"/>
+      <c r="E74" s="3" t="n"/>
+      <c r="F74" s="3" t="n"/>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+      <c r="I74" s="3" t="n"/>
+      <c r="J74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>GMP-200-230560</t>
         </is>
       </c>
-      <c r="C73" s="7" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">20 MM NAMLU ADAPTÖRÜ (V-SP) </t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>GMP-101-230036</t>
         </is>
       </c>
-      <c r="E73" s="7" t="inlineStr">
+      <c r="E75" s="7" t="inlineStr">
         <is>
           <t>20 MM NAMLU ADAPTÖRÜ (V-SP)</t>
         </is>
       </c>
-      <c r="F73" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H73" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="6" t="n"/>
-      <c r="K73" s="6" t="n"/>
-      <c r="L73" s="6" t="n"/>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="11" t="inlineStr">
+      <c r="F75" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="6" t="n"/>
+      <c r="K75" s="6" t="n"/>
+      <c r="L75" s="6" t="n"/>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B74" s="11" t="inlineStr">
+      <c r="B76" s="11" t="inlineStr">
         <is>
           <t>GMP-200-230560</t>
         </is>
       </c>
-      <c r="C74" s="12" t="inlineStr">
+      <c r="C76" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">20 MM NAMLU ADAPTÖRÜ (V-SP) </t>
         </is>
       </c>
-      <c r="D74" s="11" t="n"/>
-      <c r="E74" s="11" t="n"/>
-      <c r="F74" s="11" t="n"/>
-      <c r="G74" s="11" t="n"/>
-      <c r="H74" s="11" t="n"/>
-      <c r="I74" s="11" t="n"/>
-      <c r="J74" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" ht="6" customHeight="1"/>
-    <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="3" t="inlineStr">
+      <c r="D76" s="11" t="n"/>
+      <c r="E76" s="11" t="n"/>
+      <c r="F76" s="11" t="n"/>
+      <c r="G76" s="11" t="n"/>
+      <c r="H76" s="11" t="n"/>
+      <c r="I76" s="11" t="n"/>
+      <c r="J76" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" ht="6" customHeight="1"/>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>GMP-200-240777</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t>KAM V3 KASA</t>
         </is>
       </c>
-      <c r="D76" s="3" t="n"/>
-      <c r="E76" s="3" t="n"/>
-      <c r="F76" s="3" t="n"/>
-      <c r="G76" s="3" t="n"/>
-      <c r="H76" s="3" t="n"/>
-      <c r="I76" s="3" t="n"/>
-      <c r="J76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
+      <c r="D78" s="3" t="n"/>
+      <c r="E78" s="3" t="n"/>
+      <c r="F78" s="3" t="n"/>
+      <c r="G78" s="3" t="n"/>
+      <c r="H78" s="3" t="n"/>
+      <c r="I78" s="3" t="n"/>
+      <c r="J78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>GMP-200-240777</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>KAM V3 KASA</t>
         </is>
       </c>
-      <c r="D77" s="6" t="inlineStr">
+      <c r="D79" s="6" t="inlineStr">
         <is>
           <t>GMP-110-240777</t>
         </is>
       </c>
-      <c r="E77" s="7" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>kam v3 kasa</t>
         </is>
       </c>
-      <c r="F77" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="6" t="n"/>
-      <c r="K77" s="6" t="n"/>
-      <c r="L77" s="6" t="n"/>
-    </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="11" t="inlineStr">
+      <c r="F79" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H79" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="6" t="n"/>
+      <c r="K79" s="6" t="n"/>
+      <c r="L79" s="6" t="n"/>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B78" s="11" t="inlineStr">
+      <c r="B80" s="11" t="inlineStr">
         <is>
           <t>GMP-200-240777</t>
         </is>
       </c>
-      <c r="C78" s="12" t="inlineStr">
+      <c r="C80" s="12" t="inlineStr">
         <is>
           <t>KAM V3 KASA</t>
         </is>
       </c>
-      <c r="D78" s="11" t="n"/>
-      <c r="E78" s="11" t="n"/>
-      <c r="F78" s="11" t="n"/>
-      <c r="G78" s="11" t="n"/>
-      <c r="H78" s="11" t="n"/>
-      <c r="I78" s="11" t="n"/>
-      <c r="J78" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" ht="6" customHeight="1"/>
-    <row r="80" ht="22" customHeight="1">
-      <c r="A80" s="3" t="inlineStr">
+      <c r="D80" s="11" t="n"/>
+      <c r="E80" s="11" t="n"/>
+      <c r="F80" s="11" t="n"/>
+      <c r="G80" s="11" t="n"/>
+      <c r="H80" s="11" t="n"/>
+      <c r="I80" s="11" t="n"/>
+      <c r="J80" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" ht="6" customHeight="1"/>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>HAV-HPB001</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>HAVALI HOPARLÖR - PAKET (100 WATT)</t>
         </is>
       </c>
-      <c r="D80" s="3" t="n"/>
-      <c r="E80" s="3" t="n"/>
-      <c r="F80" s="3" t="n"/>
-      <c r="G80" s="3" t="n"/>
-      <c r="H80" s="3" t="n"/>
-      <c r="I80" s="3" t="n"/>
-      <c r="J80" s="5" t="n">
+      <c r="D82" s="3" t="n"/>
+      <c r="E82" s="3" t="n"/>
+      <c r="F82" s="3" t="n"/>
+      <c r="G82" s="3" t="n"/>
+      <c r="H82" s="3" t="n"/>
+      <c r="I82" s="3" t="n"/>
+      <c r="J82" s="5" t="n">
         <v>1322.61</v>
       </c>
-      <c r="K80" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="5" t="n">
+      <c r="K82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="5" t="n">
         <v>1322.61</v>
       </c>
     </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="inlineStr">
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
         <is>
           <t>HAV-HPB001</t>
         </is>
       </c>
-      <c r="C81" s="7" t="inlineStr">
+      <c r="C83" s="7" t="inlineStr">
         <is>
           <t>HAVALI HOPARLÖR - PAKET (100 WATT)</t>
         </is>
       </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="D83" s="6" t="inlineStr">
         <is>
           <t>HAV-HPB0001</t>
         </is>
       </c>
-      <c r="E81" s="7" t="inlineStr">
+      <c r="E83" s="7" t="inlineStr">
         <is>
           <t>HAVALI HOPARLÖR - PAKET (100 WATT)</t>
         </is>
       </c>
-      <c r="F81" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H81" s="9" t="n">
+      <c r="F83" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H83" s="9" t="n">
         <v>1322.61</v>
       </c>
-      <c r="I81" s="10" t="n">
+      <c r="I83" s="10" t="n">
         <v>1322.61</v>
       </c>
-      <c r="J81" s="6" t="n"/>
-      <c r="K81" s="6" t="n"/>
-      <c r="L81" s="6" t="n"/>
-    </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="11" t="inlineStr">
+      <c r="J83" s="6" t="n"/>
+      <c r="K83" s="6" t="n"/>
+      <c r="L83" s="6" t="n"/>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B82" s="11" t="inlineStr">
+      <c r="B84" s="11" t="inlineStr">
         <is>
           <t>HAV-HPB001</t>
         </is>
       </c>
-      <c r="C82" s="12" t="inlineStr">
+      <c r="C84" s="12" t="inlineStr">
         <is>
           <t>HAVALI HOPARLÖR - PAKET (100 WATT)</t>
         </is>
       </c>
-      <c r="D82" s="11" t="n"/>
-      <c r="E82" s="11" t="n"/>
-      <c r="F82" s="11" t="n"/>
-      <c r="G82" s="11" t="n"/>
-      <c r="H82" s="11" t="n"/>
-      <c r="I82" s="11" t="n"/>
-      <c r="J82" s="13" t="n">
+      <c r="D84" s="11" t="n"/>
+      <c r="E84" s="11" t="n"/>
+      <c r="F84" s="11" t="n"/>
+      <c r="G84" s="11" t="n"/>
+      <c r="H84" s="11" t="n"/>
+      <c r="I84" s="11" t="n"/>
+      <c r="J84" s="13" t="n">
         <v>1322.61</v>
       </c>
-      <c r="K82" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="13" t="n">
+      <c r="K84" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="13" t="n">
         <v>1322.61</v>
       </c>
     </row>
-    <row r="83" ht="6" customHeight="1"/>
-    <row r="84" ht="22" customHeight="1">
-      <c r="A84" s="3" t="inlineStr">
+    <row r="85" ht="6" customHeight="1"/>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>HAV-HPB002</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>HAVALI HOPARLÖR - PAKET (150 WATT)</t>
         </is>
       </c>
-      <c r="D84" s="3" t="n"/>
-      <c r="E84" s="3" t="n"/>
-      <c r="F84" s="3" t="n"/>
-      <c r="G84" s="3" t="n"/>
-      <c r="H84" s="3" t="n"/>
-      <c r="I84" s="3" t="n"/>
-      <c r="J84" s="5" t="n">
+      <c r="D86" s="3" t="n"/>
+      <c r="E86" s="3" t="n"/>
+      <c r="F86" s="3" t="n"/>
+      <c r="G86" s="3" t="n"/>
+      <c r="H86" s="3" t="n"/>
+      <c r="I86" s="3" t="n"/>
+      <c r="J86" s="5" t="n">
         <v>1306.79</v>
       </c>
-      <c r="K84" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="5" t="n">
+      <c r="K86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="5" t="n">
         <v>1306.79</v>
       </c>
     </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>HAV-HPB002</t>
         </is>
       </c>
-      <c r="C85" s="7" t="inlineStr">
+      <c r="C87" s="7" t="inlineStr">
         <is>
           <t>HAVALI HOPARLÖR - PAKET (150 WATT)</t>
         </is>
       </c>
-      <c r="D85" s="6" t="inlineStr">
+      <c r="D87" s="6" t="inlineStr">
         <is>
           <t>HAV-HPB0002</t>
         </is>
       </c>
-      <c r="E85" s="7" t="inlineStr">
+      <c r="E87" s="7" t="inlineStr">
         <is>
           <t>HAVALI HOPARLÖR - PAKET (150 WATT)</t>
         </is>
       </c>
-      <c r="F85" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H85" s="9" t="n">
+      <c r="F87" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H87" s="9" t="n">
         <v>1306.7923</v>
       </c>
-      <c r="I85" s="10" t="n">
+      <c r="I87" s="10" t="n">
         <v>1306.79</v>
       </c>
-      <c r="J85" s="6" t="n"/>
-      <c r="K85" s="6" t="n"/>
-      <c r="L85" s="6" t="n"/>
-    </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="11" t="inlineStr">
+      <c r="J87" s="6" t="n"/>
+      <c r="K87" s="6" t="n"/>
+      <c r="L87" s="6" t="n"/>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B86" s="11" t="inlineStr">
+      <c r="B88" s="11" t="inlineStr">
         <is>
           <t>HAV-HPB002</t>
         </is>
       </c>
-      <c r="C86" s="12" t="inlineStr">
+      <c r="C88" s="12" t="inlineStr">
         <is>
           <t>HAVALI HOPARLÖR - PAKET (150 WATT)</t>
         </is>
       </c>
-      <c r="D86" s="11" t="n"/>
-      <c r="E86" s="11" t="n"/>
-      <c r="F86" s="11" t="n"/>
-      <c r="G86" s="11" t="n"/>
-      <c r="H86" s="11" t="n"/>
-      <c r="I86" s="11" t="n"/>
-      <c r="J86" s="13" t="n">
+      <c r="D88" s="11" t="n"/>
+      <c r="E88" s="11" t="n"/>
+      <c r="F88" s="11" t="n"/>
+      <c r="G88" s="11" t="n"/>
+      <c r="H88" s="11" t="n"/>
+      <c r="I88" s="11" t="n"/>
+      <c r="J88" s="13" t="n">
         <v>1306.79</v>
       </c>
-      <c r="K86" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="13" t="n">
+      <c r="K88" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="13" t="n">
         <v>1306.79</v>
       </c>
     </row>
-    <row r="87" ht="6" customHeight="1"/>
-    <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="3" t="inlineStr">
+    <row r="89" ht="6" customHeight="1"/>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>KASA ÖN KAPAK GRUBU (SABİT (SIK) PS-10F2)</t>
         </is>
       </c>
-      <c r="C88" s="4" t="inlineStr">
+      <c r="C90" s="4" t="inlineStr">
         <is>
           <t>YMB-V00R01-220014</t>
         </is>
       </c>
-      <c r="D88" s="3" t="n"/>
-      <c r="E88" s="3" t="n"/>
-      <c r="F88" s="3" t="n"/>
-      <c r="G88" s="3" t="n"/>
-      <c r="H88" s="3" t="n"/>
-      <c r="I88" s="3" t="n"/>
-      <c r="J88" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B89" s="6" t="inlineStr">
+      <c r="D90" s="3" t="n"/>
+      <c r="E90" s="3" t="n"/>
+      <c r="F90" s="3" t="n"/>
+      <c r="G90" s="3" t="n"/>
+      <c r="H90" s="3" t="n"/>
+      <c r="I90" s="3" t="n"/>
+      <c r="J90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>KASA ÖN KAPAK GRUBU (SABİT (SIK) PS-10F2)</t>
         </is>
       </c>
-      <c r="C89" s="7" t="inlineStr">
+      <c r="C91" s="7" t="inlineStr">
         <is>
           <t>YMB-V00R01-220014</t>
         </is>
       </c>
-      <c r="D89" s="6" t="inlineStr">
+      <c r="D91" s="6" t="inlineStr">
         <is>
           <t>YMB-V00R01-220014</t>
         </is>
       </c>
-      <c r="E89" s="7" t="inlineStr">
+      <c r="E91" s="7" t="inlineStr">
         <is>
           <t>KASA ÖN KAPAK GRUBU (SABİT (SIK) PS-10F2)</t>
         </is>
       </c>
-      <c r="F89" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H89" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="6" t="n"/>
-      <c r="K89" s="6" t="n"/>
-      <c r="L89" s="6" t="n"/>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="11" t="inlineStr">
+      <c r="F91" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H91" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="6" t="n"/>
+      <c r="K91" s="6" t="n"/>
+      <c r="L91" s="6" t="n"/>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B90" s="11" t="inlineStr">
+      <c r="B92" s="11" t="inlineStr">
         <is>
           <t>KASA ÖN KAPAK GRUBU (SABİT (SIK) PS-10F2)</t>
         </is>
       </c>
-      <c r="C90" s="12" t="inlineStr">
+      <c r="C92" s="12" t="inlineStr">
         <is>
           <t>YMB-V00R01-220014</t>
         </is>
       </c>
-      <c r="D90" s="11" t="n"/>
-      <c r="E90" s="11" t="n"/>
-      <c r="F90" s="11" t="n"/>
-      <c r="G90" s="11" t="n"/>
-      <c r="H90" s="11" t="n"/>
-      <c r="I90" s="11" t="n"/>
-      <c r="J90" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" ht="6" customHeight="1"/>
-    <row r="92" ht="22" customHeight="1">
-      <c r="A92" s="3" t="inlineStr">
+      <c r="D92" s="11" t="n"/>
+      <c r="E92" s="11" t="n"/>
+      <c r="F92" s="11" t="n"/>
+      <c r="G92" s="11" t="n"/>
+      <c r="H92" s="11" t="n"/>
+      <c r="I92" s="11" t="n"/>
+      <c r="J92" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" ht="6" customHeight="1"/>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>MEK-V00R00-220025</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
+      <c r="C94" s="4" t="inlineStr">
         <is>
           <t>OLED LENS RETAİNER</t>
         </is>
       </c>
-      <c r="D92" s="3" t="n"/>
-      <c r="E92" s="3" t="n"/>
-      <c r="F92" s="3" t="n"/>
-      <c r="G92" s="3" t="n"/>
-      <c r="H92" s="3" t="n"/>
-      <c r="I92" s="3" t="n"/>
-      <c r="J92" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="D94" s="3" t="n"/>
+      <c r="E94" s="3" t="n"/>
+      <c r="F94" s="3" t="n"/>
+      <c r="G94" s="3" t="n"/>
+      <c r="H94" s="3" t="n"/>
+      <c r="I94" s="3" t="n"/>
+      <c r="J94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
         <is>
           <t>MEK-V00R00-220025</t>
         </is>
       </c>
-      <c r="C93" s="7" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>OLED LENS RETAİNER</t>
         </is>
       </c>
-      <c r="D93" s="6" t="inlineStr">
+      <c r="D95" s="6" t="inlineStr">
         <is>
           <t>MEK-VOOROO-220025</t>
         </is>
       </c>
-      <c r="E93" s="7" t="inlineStr">
+      <c r="E95" s="7" t="inlineStr">
         <is>
           <t>OLED_LENS-RETAINER</t>
         </is>
       </c>
-      <c r="F93" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" s="6" t="n"/>
-      <c r="K93" s="6" t="n"/>
-      <c r="L93" s="6" t="n"/>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="11" t="inlineStr">
+      <c r="F95" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="6" t="n"/>
+      <c r="K95" s="6" t="n"/>
+      <c r="L95" s="6" t="n"/>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B94" s="11" t="inlineStr">
+      <c r="B96" s="11" t="inlineStr">
         <is>
           <t>MEK-V00R00-220025</t>
         </is>
       </c>
-      <c r="C94" s="12" t="inlineStr">
+      <c r="C96" s="12" t="inlineStr">
         <is>
           <t>OLED LENS RETAİNER</t>
         </is>
       </c>
-      <c r="D94" s="11" t="n"/>
-      <c r="E94" s="11" t="n"/>
-      <c r="F94" s="11" t="n"/>
-      <c r="G94" s="11" t="n"/>
-      <c r="H94" s="11" t="n"/>
-      <c r="I94" s="11" t="n"/>
-      <c r="J94" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" ht="6" customHeight="1"/>
-    <row r="96" ht="22" customHeight="1">
-      <c r="A96" s="3" t="inlineStr">
+      <c r="D96" s="11" t="n"/>
+      <c r="E96" s="11" t="n"/>
+      <c r="F96" s="11" t="n"/>
+      <c r="G96" s="11" t="n"/>
+      <c r="H96" s="11" t="n"/>
+      <c r="I96" s="11" t="n"/>
+      <c r="J96" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" ht="6" customHeight="1"/>
+    <row r="98" ht="22" customHeight="1">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B96" s="3" t="inlineStr">
+      <c r="B98" s="3" t="inlineStr">
         <is>
           <t>MEK-V00R00-220044</t>
         </is>
       </c>
-      <c r="C96" s="4" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>SOĞUTUCU TEFLON</t>
         </is>
       </c>
-      <c r="D96" s="3" t="n"/>
-      <c r="E96" s="3" t="n"/>
-      <c r="F96" s="3" t="n"/>
-      <c r="G96" s="3" t="n"/>
-      <c r="H96" s="3" t="n"/>
-      <c r="I96" s="3" t="n"/>
-      <c r="J96" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="D98" s="3" t="n"/>
+      <c r="E98" s="3" t="n"/>
+      <c r="F98" s="3" t="n"/>
+      <c r="G98" s="3" t="n"/>
+      <c r="H98" s="3" t="n"/>
+      <c r="I98" s="3" t="n"/>
+      <c r="J98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
         <is>
           <t>MEK-V00R00-220044</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr">
+      <c r="C99" s="7" t="inlineStr">
         <is>
           <t>SOĞUTUCU TEFLON</t>
         </is>
       </c>
-      <c r="D97" s="6" t="inlineStr">
+      <c r="D99" s="6" t="inlineStr">
         <is>
           <t>GMP-200-230051</t>
         </is>
       </c>
-      <c r="E97" s="7" t="inlineStr">
+      <c r="E99" s="7" t="inlineStr">
         <is>
           <t>SOĞUTUCU TEFLON (MEK-V00R00-220044)</t>
         </is>
       </c>
-      <c r="F97" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G97" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="6" t="n"/>
-      <c r="K97" s="6" t="n"/>
-      <c r="L97" s="6" t="n"/>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="11" t="inlineStr">
+      <c r="F99" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H99" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="6" t="n"/>
+      <c r="K99" s="6" t="n"/>
+      <c r="L99" s="6" t="n"/>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B98" s="11" t="inlineStr">
+      <c r="B100" s="11" t="inlineStr">
         <is>
           <t>MEK-V00R00-220044</t>
         </is>
       </c>
-      <c r="C98" s="12" t="inlineStr">
+      <c r="C100" s="12" t="inlineStr">
         <is>
           <t>SOĞUTUCU TEFLON</t>
         </is>
       </c>
-      <c r="D98" s="11" t="n"/>
-      <c r="E98" s="11" t="n"/>
-      <c r="F98" s="11" t="n"/>
-      <c r="G98" s="11" t="n"/>
-      <c r="H98" s="11" t="n"/>
-      <c r="I98" s="11" t="n"/>
-      <c r="J98" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" ht="6" customHeight="1"/>
-    <row r="100" ht="22" customHeight="1">
-      <c r="A100" s="3" t="inlineStr">
+      <c r="D100" s="11" t="n"/>
+      <c r="E100" s="11" t="n"/>
+      <c r="F100" s="11" t="n"/>
+      <c r="G100" s="11" t="n"/>
+      <c r="H100" s="11" t="n"/>
+      <c r="I100" s="11" t="n"/>
+      <c r="J100" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" ht="6" customHeight="1"/>
+    <row r="102" ht="22" customHeight="1">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t>MMBMB00001</t>
         </is>
       </c>
-      <c r="C100" s="4" t="inlineStr">
+      <c r="C102" s="4" t="inlineStr">
         <is>
           <t>İP VE KANCA SETİ MEKANİK EKİPMANLARI</t>
         </is>
       </c>
-      <c r="D100" s="3" t="n"/>
-      <c r="E100" s="3" t="n"/>
-      <c r="F100" s="3" t="n"/>
-      <c r="G100" s="3" t="n"/>
-      <c r="H100" s="3" t="n"/>
-      <c r="I100" s="3" t="n"/>
-      <c r="J100" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" ht="18" customHeight="1">
-      <c r="A101" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
+      <c r="D102" s="3" t="n"/>
+      <c r="E102" s="3" t="n"/>
+      <c r="F102" s="3" t="n"/>
+      <c r="G102" s="3" t="n"/>
+      <c r="H102" s="3" t="n"/>
+      <c r="I102" s="3" t="n"/>
+      <c r="J102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
         <is>
           <t>MMBMB00001</t>
         </is>
       </c>
-      <c r="C101" s="7" t="inlineStr">
+      <c r="C103" s="7" t="inlineStr">
         <is>
           <t>İP VE KANCA SETİ MEKANİK EKİPMANLARI</t>
         </is>
       </c>
-      <c r="D101" s="6" t="inlineStr">
+      <c r="D103" s="6" t="inlineStr">
         <is>
           <t>GMP-101-230046</t>
         </is>
       </c>
-      <c r="E101" s="7" t="inlineStr">
+      <c r="E103" s="7" t="inlineStr">
         <is>
           <t>İP VE KANCA SETİ MEKANİK EKİPMANLARI</t>
         </is>
       </c>
-      <c r="F101" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G101" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" s="6" t="n"/>
-      <c r="K101" s="6" t="n"/>
-      <c r="L101" s="6" t="n"/>
-    </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="11" t="inlineStr">
+      <c r="F103" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="6" t="n"/>
+      <c r="K103" s="6" t="n"/>
+      <c r="L103" s="6" t="n"/>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B102" s="11" t="inlineStr">
+      <c r="B104" s="11" t="inlineStr">
         <is>
           <t>MMBMB00001</t>
         </is>
       </c>
-      <c r="C102" s="12" t="inlineStr">
+      <c r="C104" s="12" t="inlineStr">
         <is>
           <t>İP VE KANCA SETİ MEKANİK EKİPMANLARI</t>
         </is>
       </c>
-      <c r="D102" s="11" t="n"/>
-      <c r="E102" s="11" t="n"/>
-      <c r="F102" s="11" t="n"/>
-      <c r="G102" s="11" t="n"/>
-      <c r="H102" s="11" t="n"/>
-      <c r="I102" s="11" t="n"/>
-      <c r="J102" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" ht="6" customHeight="1"/>
-    <row r="104" ht="22" customHeight="1">
-      <c r="A104" s="3" t="inlineStr">
+      <c r="D104" s="11" t="n"/>
+      <c r="E104" s="11" t="n"/>
+      <c r="F104" s="11" t="n"/>
+      <c r="G104" s="11" t="n"/>
+      <c r="H104" s="11" t="n"/>
+      <c r="I104" s="11" t="n"/>
+      <c r="J104" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" ht="6" customHeight="1"/>
+    <row r="106" ht="22" customHeight="1">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B104" s="3" t="inlineStr">
+      <c r="B106" s="3" t="inlineStr">
         <is>
           <t>MMBMB00002</t>
         </is>
       </c>
-      <c r="C104" s="4" t="inlineStr">
+      <c r="C106" s="4" t="inlineStr">
         <is>
           <t>İP VE KANCA SETİ BİNA KİTİ MEKANİK EKİPMANLARI</t>
         </is>
       </c>
-      <c r="D104" s="3" t="n"/>
-      <c r="E104" s="3" t="n"/>
-      <c r="F104" s="3" t="n"/>
-      <c r="G104" s="3" t="n"/>
-      <c r="H104" s="3" t="n"/>
-      <c r="I104" s="3" t="n"/>
-      <c r="J104" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="A105" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B105" s="6" t="inlineStr">
+      <c r="D106" s="3" t="n"/>
+      <c r="E106" s="3" t="n"/>
+      <c r="F106" s="3" t="n"/>
+      <c r="G106" s="3" t="n"/>
+      <c r="H106" s="3" t="n"/>
+      <c r="I106" s="3" t="n"/>
+      <c r="J106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>MMBMB00002</t>
         </is>
       </c>
-      <c r="C105" s="7" t="inlineStr">
+      <c r="C107" s="7" t="inlineStr">
         <is>
           <t>İP VE KANCA SETİ BİNA KİTİ MEKANİK EKİPMANLARI</t>
         </is>
       </c>
-      <c r="D105" s="6" t="inlineStr">
+      <c r="D107" s="6" t="inlineStr">
         <is>
           <t>GMP-101-230047</t>
         </is>
       </c>
-      <c r="E105" s="7" t="inlineStr">
+      <c r="E107" s="7" t="inlineStr">
         <is>
           <t>İP VE KANCA SETİ BİNA KİTİ MEKANİK EKİPMANLARI</t>
         </is>
       </c>
-      <c r="F105" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G105" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" s="6" t="n"/>
-      <c r="K105" s="6" t="n"/>
-      <c r="L105" s="6" t="n"/>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="11" t="inlineStr">
+      <c r="F107" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="6" t="n"/>
+      <c r="K107" s="6" t="n"/>
+      <c r="L107" s="6" t="n"/>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B106" s="11" t="inlineStr">
+      <c r="B108" s="11" t="inlineStr">
         <is>
           <t>MMBMB00002</t>
         </is>
       </c>
-      <c r="C106" s="12" t="inlineStr">
+      <c r="C108" s="12" t="inlineStr">
         <is>
           <t>İP VE KANCA SETİ BİNA KİTİ MEKANİK EKİPMANLARI</t>
         </is>
       </c>
-      <c r="D106" s="11" t="n"/>
-      <c r="E106" s="11" t="n"/>
-      <c r="F106" s="11" t="n"/>
-      <c r="G106" s="11" t="n"/>
-      <c r="H106" s="11" t="n"/>
-      <c r="I106" s="11" t="n"/>
-      <c r="J106" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" ht="6" customHeight="1"/>
-    <row r="108" ht="22" customHeight="1">
-      <c r="A108" s="3" t="inlineStr">
+      <c r="D108" s="11" t="n"/>
+      <c r="E108" s="11" t="n"/>
+      <c r="F108" s="11" t="n"/>
+      <c r="G108" s="11" t="n"/>
+      <c r="H108" s="11" t="n"/>
+      <c r="I108" s="11" t="n"/>
+      <c r="J108" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" ht="6" customHeight="1"/>
+    <row r="110" ht="22" customHeight="1">
+      <c r="A110" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B108" s="3" t="inlineStr">
+      <c r="B110" s="3" t="inlineStr">
         <is>
           <t>MMBMB00003</t>
         </is>
       </c>
-      <c r="C108" s="4" t="inlineStr">
+      <c r="C110" s="4" t="inlineStr">
         <is>
           <t>İP VE KANCA SETİ ARAÇ KİTİ MEKANİK EKİPMANLARI</t>
         </is>
       </c>
-      <c r="D108" s="3" t="n"/>
-      <c r="E108" s="3" t="n"/>
-      <c r="F108" s="3" t="n"/>
-      <c r="G108" s="3" t="n"/>
-      <c r="H108" s="3" t="n"/>
-      <c r="I108" s="3" t="n"/>
-      <c r="J108" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="A109" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B109" s="6" t="inlineStr">
+      <c r="D110" s="3" t="n"/>
+      <c r="E110" s="3" t="n"/>
+      <c r="F110" s="3" t="n"/>
+      <c r="G110" s="3" t="n"/>
+      <c r="H110" s="3" t="n"/>
+      <c r="I110" s="3" t="n"/>
+      <c r="J110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
         <is>
           <t>MMBMB00003</t>
         </is>
       </c>
-      <c r="C109" s="7" t="inlineStr">
+      <c r="C111" s="7" t="inlineStr">
         <is>
           <t>İP VE KANCA SETİ ARAÇ KİTİ MEKANİK EKİPMANLARI</t>
         </is>
       </c>
-      <c r="D109" s="6" t="inlineStr">
+      <c r="D111" s="6" t="inlineStr">
         <is>
           <t>GMP-101-230048</t>
         </is>
       </c>
-      <c r="E109" s="7" t="inlineStr">
+      <c r="E111" s="7" t="inlineStr">
         <is>
           <t>İP VE KANCA SETİ ARAÇ KİTİ MEKANİK EKİPMANLARI</t>
         </is>
       </c>
-      <c r="F109" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G109" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" s="6" t="n"/>
-      <c r="K109" s="6" t="n"/>
-      <c r="L109" s="6" t="n"/>
-    </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="11" t="inlineStr">
+      <c r="F111" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" s="6" t="n"/>
+      <c r="K111" s="6" t="n"/>
+      <c r="L111" s="6" t="n"/>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B110" s="11" t="inlineStr">
+      <c r="B112" s="11" t="inlineStr">
         <is>
           <t>MMBMB00003</t>
         </is>
       </c>
-      <c r="C110" s="12" t="inlineStr">
+      <c r="C112" s="12" t="inlineStr">
         <is>
           <t>İP VE KANCA SETİ ARAÇ KİTİ MEKANİK EKİPMANLARI</t>
         </is>
       </c>
-      <c r="D110" s="11" t="n"/>
-      <c r="E110" s="11" t="n"/>
-      <c r="F110" s="11" t="n"/>
-      <c r="G110" s="11" t="n"/>
-      <c r="H110" s="11" t="n"/>
-      <c r="I110" s="11" t="n"/>
-      <c r="J110" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K110" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" ht="6" customHeight="1"/>
-    <row r="112" ht="22" customHeight="1">
-      <c r="A112" s="3" t="inlineStr">
+      <c r="D112" s="11" t="n"/>
+      <c r="E112" s="11" t="n"/>
+      <c r="F112" s="11" t="n"/>
+      <c r="G112" s="11" t="n"/>
+      <c r="H112" s="11" t="n"/>
+      <c r="I112" s="11" t="n"/>
+      <c r="J112" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" ht="6" customHeight="1"/>
+    <row r="114" ht="22" customHeight="1">
+      <c r="A114" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B112" s="3" t="inlineStr">
+      <c r="B114" s="3" t="inlineStr">
         <is>
           <t>MMBRSCOBE01</t>
         </is>
       </c>
-      <c r="C112" s="4" t="inlineStr">
+      <c r="C114" s="4" t="inlineStr">
         <is>
           <t>BORESCOPE</t>
         </is>
       </c>
-      <c r="D112" s="3" t="n"/>
-      <c r="E112" s="3" t="n"/>
-      <c r="F112" s="3" t="n"/>
-      <c r="G112" s="3" t="n"/>
-      <c r="H112" s="3" t="n"/>
-      <c r="I112" s="3" t="n"/>
-      <c r="J112" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K112" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" ht="18" customHeight="1">
-      <c r="A113" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B113" s="6" t="inlineStr">
+      <c r="D114" s="3" t="n"/>
+      <c r="E114" s="3" t="n"/>
+      <c r="F114" s="3" t="n"/>
+      <c r="G114" s="3" t="n"/>
+      <c r="H114" s="3" t="n"/>
+      <c r="I114" s="3" t="n"/>
+      <c r="J114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
         <is>
           <t>MMBRSCOBE01</t>
         </is>
       </c>
-      <c r="C113" s="7" t="inlineStr">
+      <c r="C115" s="7" t="inlineStr">
         <is>
           <t>BORESCOPE</t>
         </is>
       </c>
-      <c r="D113" s="6" t="inlineStr">
+      <c r="D115" s="6" t="inlineStr">
         <is>
           <t>GMP-101-230050</t>
         </is>
       </c>
-      <c r="E113" s="7" t="inlineStr">
+      <c r="E115" s="7" t="inlineStr">
         <is>
           <t>8X L TİPİ BORESCOPE (12.7 MM X 40 MM NİŞAN AYAR APARATI İLE)</t>
         </is>
       </c>
-      <c r="F113" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G113" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H113" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" s="6" t="n"/>
-      <c r="K113" s="6" t="n"/>
-      <c r="L113" s="6" t="n"/>
-    </row>
-    <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="11" t="inlineStr">
+      <c r="F115" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="6" t="n"/>
+      <c r="K115" s="6" t="n"/>
+      <c r="L115" s="6" t="n"/>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B114" s="11" t="inlineStr">
+      <c r="B116" s="11" t="inlineStr">
         <is>
           <t>MMBRSCOBE01</t>
         </is>
       </c>
-      <c r="C114" s="12" t="inlineStr">
+      <c r="C116" s="12" t="inlineStr">
         <is>
           <t>BORESCOPE</t>
         </is>
       </c>
-      <c r="D114" s="11" t="n"/>
-      <c r="E114" s="11" t="n"/>
-      <c r="F114" s="11" t="n"/>
-      <c r="G114" s="11" t="n"/>
-      <c r="H114" s="11" t="n"/>
-      <c r="I114" s="11" t="n"/>
-      <c r="J114" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" ht="6" customHeight="1"/>
-    <row r="116" ht="22" customHeight="1">
-      <c r="A116" s="3" t="inlineStr">
+      <c r="D116" s="11" t="n"/>
+      <c r="E116" s="11" t="n"/>
+      <c r="F116" s="11" t="n"/>
+      <c r="G116" s="11" t="n"/>
+      <c r="H116" s="11" t="n"/>
+      <c r="I116" s="11" t="n"/>
+      <c r="J116" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" ht="6" customHeight="1"/>
+    <row r="118" ht="22" customHeight="1">
+      <c r="A118" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B116" s="3" t="inlineStr">
+      <c r="B118" s="3" t="inlineStr">
         <is>
           <t>MMCC0000001</t>
         </is>
       </c>
-      <c r="C116" s="4" t="inlineStr">
+      <c r="C118" s="4" t="inlineStr">
         <is>
           <t>TX IR-610 CC VERİCİ-TELSİZSİZ</t>
         </is>
       </c>
-      <c r="D116" s="3" t="n"/>
-      <c r="E116" s="3" t="n"/>
-      <c r="F116" s="3" t="n"/>
-      <c r="G116" s="3" t="n"/>
-      <c r="H116" s="3" t="n"/>
-      <c r="I116" s="3" t="n"/>
-      <c r="J116" s="5" t="n">
+      <c r="D118" s="3" t="n"/>
+      <c r="E118" s="3" t="n"/>
+      <c r="F118" s="3" t="n"/>
+      <c r="G118" s="3" t="n"/>
+      <c r="H118" s="3" t="n"/>
+      <c r="I118" s="3" t="n"/>
+      <c r="J118" s="5" t="n">
         <v>10121.22</v>
       </c>
-      <c r="K116" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="5" t="n">
+      <c r="K118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="5" t="n">
         <v>10121.22</v>
       </c>
     </row>
-    <row r="117" ht="18" customHeight="1">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr">
+    <row r="119" ht="18" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
         <is>
           <t>MMCC0000001</t>
         </is>
       </c>
-      <c r="C117" s="7" t="inlineStr">
+      <c r="C119" s="7" t="inlineStr">
         <is>
           <t>TX IR-610 CC VERİCİ-TELSİZSİZ</t>
         </is>
       </c>
-      <c r="D117" s="6" t="inlineStr">
+      <c r="D119" s="6" t="inlineStr">
         <is>
           <t>GMP-101-230051</t>
         </is>
       </c>
-      <c r="E117" s="7" t="inlineStr">
+      <c r="E119" s="7" t="inlineStr">
         <is>
           <t>TX IR-610 CC VERİCİ-TELSİZSİZ</t>
         </is>
       </c>
-      <c r="F117" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G117" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H117" s="9" t="n">
+      <c r="F119" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H119" s="9" t="n">
         <v>10121.22</v>
       </c>
-      <c r="I117" s="10" t="n">
+      <c r="I119" s="10" t="n">
         <v>10121.22</v>
       </c>
-      <c r="J117" s="6" t="n"/>
-      <c r="K117" s="6" t="n"/>
-      <c r="L117" s="6" t="n"/>
-    </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="11" t="inlineStr">
+      <c r="J119" s="6" t="n"/>
+      <c r="K119" s="6" t="n"/>
+      <c r="L119" s="6" t="n"/>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B118" s="11" t="inlineStr">
+      <c r="B120" s="11" t="inlineStr">
         <is>
           <t>MMCC0000001</t>
         </is>
       </c>
-      <c r="C118" s="12" t="inlineStr">
+      <c r="C120" s="12" t="inlineStr">
         <is>
           <t>TX IR-610 CC VERİCİ-TELSİZSİZ</t>
         </is>
       </c>
-      <c r="D118" s="11" t="n"/>
-      <c r="E118" s="11" t="n"/>
-      <c r="F118" s="11" t="n"/>
-      <c r="G118" s="11" t="n"/>
-      <c r="H118" s="11" t="n"/>
-      <c r="I118" s="11" t="n"/>
-      <c r="J118" s="13" t="n">
+      <c r="D120" s="11" t="n"/>
+      <c r="E120" s="11" t="n"/>
+      <c r="F120" s="11" t="n"/>
+      <c r="G120" s="11" t="n"/>
+      <c r="H120" s="11" t="n"/>
+      <c r="I120" s="11" t="n"/>
+      <c r="J120" s="13" t="n">
         <v>10121.22</v>
       </c>
-      <c r="K118" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" s="13" t="n">
+      <c r="K120" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="13" t="n">
         <v>10121.22</v>
       </c>
     </row>
-    <row r="119" ht="6" customHeight="1"/>
-    <row r="120" ht="22" customHeight="1">
-      <c r="A120" s="3" t="inlineStr">
+    <row r="121" ht="6" customHeight="1"/>
+    <row r="122" ht="22" customHeight="1">
+      <c r="A122" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B120" s="3" t="inlineStr">
+      <c r="B122" s="3" t="inlineStr">
         <is>
           <t>MMGM500003</t>
         </is>
       </c>
-      <c r="C120" s="4" t="inlineStr">
+      <c r="C122" s="4" t="inlineStr">
         <is>
           <t>VK SABİT MERKEZ VERİCİ-TELSİZSİZ</t>
         </is>
       </c>
-      <c r="D120" s="3" t="n"/>
-      <c r="E120" s="3" t="n"/>
-      <c r="F120" s="3" t="n"/>
-      <c r="G120" s="3" t="n"/>
-      <c r="H120" s="3" t="n"/>
-      <c r="I120" s="3" t="n"/>
-      <c r="J120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" ht="18" customHeight="1">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B121" s="6" t="inlineStr">
+      <c r="D122" s="3" t="n"/>
+      <c r="E122" s="3" t="n"/>
+      <c r="F122" s="3" t="n"/>
+      <c r="G122" s="3" t="n"/>
+      <c r="H122" s="3" t="n"/>
+      <c r="I122" s="3" t="n"/>
+      <c r="J122" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
         <is>
           <t>MMGM500003</t>
         </is>
       </c>
-      <c r="C121" s="7" t="inlineStr">
+      <c r="C123" s="7" t="inlineStr">
         <is>
           <t>VK SABİT MERKEZ VERİCİ-TELSİZSİZ</t>
         </is>
       </c>
-      <c r="D121" s="6" t="inlineStr">
+      <c r="D123" s="6" t="inlineStr">
         <is>
           <t>GMP-101-230061</t>
         </is>
       </c>
-      <c r="E121" s="7" t="inlineStr">
+      <c r="E123" s="7" t="inlineStr">
         <is>
           <t>VK SABİT MERKEZ VERİCİ-TELSİZSİZ</t>
         </is>
       </c>
-      <c r="F121" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G121" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I121" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" s="6" t="n"/>
-      <c r="K121" s="6" t="n"/>
-      <c r="L121" s="6" t="n"/>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="11" t="inlineStr">
+      <c r="F123" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="6" t="n"/>
+      <c r="K123" s="6" t="n"/>
+      <c r="L123" s="6" t="n"/>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B122" s="11" t="inlineStr">
+      <c r="B124" s="11" t="inlineStr">
         <is>
           <t>MMGM500003</t>
         </is>
       </c>
-      <c r="C122" s="12" t="inlineStr">
+      <c r="C124" s="12" t="inlineStr">
         <is>
           <t>VK SABİT MERKEZ VERİCİ-TELSİZSİZ</t>
         </is>
       </c>
-      <c r="D122" s="11" t="n"/>
-      <c r="E122" s="11" t="n"/>
-      <c r="F122" s="11" t="n"/>
-      <c r="G122" s="11" t="n"/>
-      <c r="H122" s="11" t="n"/>
-      <c r="I122" s="11" t="n"/>
-      <c r="J122" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" ht="6" customHeight="1"/>
-    <row r="124" ht="22" customHeight="1">
-      <c r="A124" s="3" t="inlineStr">
+      <c r="D124" s="11" t="n"/>
+      <c r="E124" s="11" t="n"/>
+      <c r="F124" s="11" t="n"/>
+      <c r="G124" s="11" t="n"/>
+      <c r="H124" s="11" t="n"/>
+      <c r="I124" s="11" t="n"/>
+      <c r="J124" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" ht="6" customHeight="1"/>
+    <row r="126" ht="22" customHeight="1">
+      <c r="A126" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B124" s="3" t="inlineStr">
+      <c r="B126" s="3" t="inlineStr">
         <is>
           <t>MMGMIR61001</t>
         </is>
       </c>
-      <c r="C124" s="4" t="inlineStr">
+      <c r="C126" s="4" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 VHF ALICI</t>
         </is>
       </c>
-      <c r="D124" s="3" t="n"/>
-      <c r="E124" s="3" t="n"/>
-      <c r="F124" s="3" t="n"/>
-      <c r="G124" s="3" t="n"/>
-      <c r="H124" s="3" t="n"/>
-      <c r="I124" s="3" t="n"/>
-      <c r="J124" s="5" t="n">
+      <c r="D126" s="3" t="n"/>
+      <c r="E126" s="3" t="n"/>
+      <c r="F126" s="3" t="n"/>
+      <c r="G126" s="3" t="n"/>
+      <c r="H126" s="3" t="n"/>
+      <c r="I126" s="3" t="n"/>
+      <c r="J126" s="5" t="n">
         <v>3239.29</v>
       </c>
-      <c r="K124" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="5" t="n">
+      <c r="K126" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="5" t="n">
         <v>3239.29</v>
       </c>
     </row>
-    <row r="125" ht="18" customHeight="1">
-      <c r="A125" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B125" s="6" t="inlineStr">
+    <row r="127" ht="18" customHeight="1">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
         <is>
           <t>MMGMIR61001</t>
         </is>
       </c>
-      <c r="C125" s="7" t="inlineStr">
+      <c r="C127" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 VHF ALICI</t>
         </is>
       </c>
-      <c r="D125" s="6" t="inlineStr">
+      <c r="D127" s="6" t="inlineStr">
         <is>
           <t>GMP-101-230063</t>
         </is>
       </c>
-      <c r="E125" s="7" t="inlineStr">
+      <c r="E127" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 VHF ALICI</t>
         </is>
       </c>
-      <c r="F125" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G125" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H125" s="9" t="n">
+      <c r="F127" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H127" s="9" t="n">
         <v>3239.2914</v>
       </c>
-      <c r="I125" s="10" t="n">
+      <c r="I127" s="10" t="n">
         <v>3239.29</v>
       </c>
-      <c r="J125" s="6" t="n"/>
-      <c r="K125" s="6" t="n"/>
-      <c r="L125" s="6" t="n"/>
-    </row>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="11" t="inlineStr">
+      <c r="J127" s="6" t="n"/>
+      <c r="K127" s="6" t="n"/>
+      <c r="L127" s="6" t="n"/>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B126" s="11" t="inlineStr">
+      <c r="B128" s="11" t="inlineStr">
         <is>
           <t>MMGMIR61001</t>
         </is>
       </c>
-      <c r="C126" s="12" t="inlineStr">
+      <c r="C128" s="12" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 VHF ALICI</t>
         </is>
       </c>
-      <c r="D126" s="11" t="n"/>
-      <c r="E126" s="11" t="n"/>
-      <c r="F126" s="11" t="n"/>
-      <c r="G126" s="11" t="n"/>
-      <c r="H126" s="11" t="n"/>
-      <c r="I126" s="11" t="n"/>
-      <c r="J126" s="13" t="n">
+      <c r="D128" s="11" t="n"/>
+      <c r="E128" s="11" t="n"/>
+      <c r="F128" s="11" t="n"/>
+      <c r="G128" s="11" t="n"/>
+      <c r="H128" s="11" t="n"/>
+      <c r="I128" s="11" t="n"/>
+      <c r="J128" s="13" t="n">
         <v>3239.29</v>
       </c>
-      <c r="K126" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" s="13" t="n">
+      <c r="K128" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="13" t="n">
         <v>3239.29</v>
       </c>
     </row>
-    <row r="127" ht="6" customHeight="1"/>
-    <row r="128" ht="22" customHeight="1">
-      <c r="A128" s="3" t="inlineStr">
+    <row r="129" ht="6" customHeight="1"/>
+    <row r="130" ht="22" customHeight="1">
+      <c r="A130" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B128" s="3" t="inlineStr">
+      <c r="B130" s="3" t="inlineStr">
         <is>
           <t>MMGMIR61002</t>
         </is>
       </c>
-      <c r="C128" s="4" t="inlineStr">
+      <c r="C130" s="4" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 UHF ALICI</t>
         </is>
       </c>
-      <c r="D128" s="3" t="n"/>
-      <c r="E128" s="3" t="n"/>
-      <c r="F128" s="3" t="n"/>
-      <c r="G128" s="3" t="n"/>
-      <c r="H128" s="3" t="n"/>
-      <c r="I128" s="3" t="n"/>
-      <c r="J128" s="5" t="n">
+      <c r="D130" s="3" t="n"/>
+      <c r="E130" s="3" t="n"/>
+      <c r="F130" s="3" t="n"/>
+      <c r="G130" s="3" t="n"/>
+      <c r="H130" s="3" t="n"/>
+      <c r="I130" s="3" t="n"/>
+      <c r="J130" s="5" t="n">
         <v>4010.8</v>
       </c>
-      <c r="K128" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" s="5" t="n">
+      <c r="K130" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" s="5" t="n">
         <v>4010.8</v>
       </c>
     </row>
-    <row r="129" ht="18" customHeight="1">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
+    <row r="131" ht="18" customHeight="1">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
         <is>
           <t>MMGMIR61002</t>
         </is>
       </c>
-      <c r="C129" s="7" t="inlineStr">
+      <c r="C131" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 UHF ALICI</t>
         </is>
       </c>
-      <c r="D129" s="6" t="inlineStr">
+      <c r="D131" s="6" t="inlineStr">
         <is>
           <t>GMP-101-230064</t>
         </is>
       </c>
-      <c r="E129" s="7" t="inlineStr">
+      <c r="E131" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 UHF ALICI</t>
         </is>
       </c>
-      <c r="F129" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G129" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H129" s="9" t="n">
+      <c r="F131" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H131" s="9" t="n">
         <v>4010.8003</v>
       </c>
-      <c r="I129" s="10" t="n">
+      <c r="I131" s="10" t="n">
         <v>4010.8</v>
       </c>
-      <c r="J129" s="6" t="n"/>
-      <c r="K129" s="6" t="n"/>
-      <c r="L129" s="6" t="n"/>
-    </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="11" t="inlineStr">
+      <c r="J131" s="6" t="n"/>
+      <c r="K131" s="6" t="n"/>
+      <c r="L131" s="6" t="n"/>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B130" s="11" t="inlineStr">
+      <c r="B132" s="11" t="inlineStr">
         <is>
           <t>MMGMIR61002</t>
         </is>
       </c>
-      <c r="C130" s="12" t="inlineStr">
+      <c r="C132" s="12" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 UHF ALICI</t>
         </is>
       </c>
-      <c r="D130" s="11" t="n"/>
-      <c r="E130" s="11" t="n"/>
-      <c r="F130" s="11" t="n"/>
-      <c r="G130" s="11" t="n"/>
-      <c r="H130" s="11" t="n"/>
-      <c r="I130" s="11" t="n"/>
-      <c r="J130" s="13" t="n">
+      <c r="D132" s="11" t="n"/>
+      <c r="E132" s="11" t="n"/>
+      <c r="F132" s="11" t="n"/>
+      <c r="G132" s="11" t="n"/>
+      <c r="H132" s="11" t="n"/>
+      <c r="I132" s="11" t="n"/>
+      <c r="J132" s="13" t="n">
         <v>4010.8</v>
       </c>
-      <c r="K130" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L130" s="13" t="n">
+      <c r="K132" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" s="13" t="n">
         <v>4010.8</v>
       </c>
     </row>
-    <row r="131" ht="6" customHeight="1"/>
-    <row r="132" ht="22" customHeight="1">
-      <c r="A132" s="3" t="inlineStr">
+    <row r="133" ht="6" customHeight="1"/>
+    <row r="134" ht="22" customHeight="1">
+      <c r="A134" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B132" s="3" t="inlineStr">
+      <c r="B134" s="3" t="inlineStr">
         <is>
           <t>MMGMIR61003</t>
         </is>
       </c>
-      <c r="C132" s="4" t="inlineStr">
+      <c r="C134" s="4" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 VHF CAMİİ ALICI</t>
         </is>
       </c>
-      <c r="D132" s="3" t="n"/>
-      <c r="E132" s="3" t="n"/>
-      <c r="F132" s="3" t="n"/>
-      <c r="G132" s="3" t="n"/>
-      <c r="H132" s="3" t="n"/>
-      <c r="I132" s="3" t="n"/>
-      <c r="J132" s="5" t="n">
+      <c r="D134" s="3" t="n"/>
+      <c r="E134" s="3" t="n"/>
+      <c r="F134" s="3" t="n"/>
+      <c r="G134" s="3" t="n"/>
+      <c r="H134" s="3" t="n"/>
+      <c r="I134" s="3" t="n"/>
+      <c r="J134" s="5" t="n">
         <v>5433.1</v>
       </c>
-      <c r="K132" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" s="5" t="n">
+      <c r="K134" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" s="5" t="n">
         <v>5433.1</v>
       </c>
     </row>
-    <row r="133" ht="18" customHeight="1">
-      <c r="A133" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B133" s="6" t="inlineStr">
+    <row r="135" ht="18" customHeight="1">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
         <is>
           <t>MMGMIR61003</t>
         </is>
       </c>
-      <c r="C133" s="7" t="inlineStr">
+      <c r="C135" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 VHF CAMİİ ALICI</t>
         </is>
       </c>
-      <c r="D133" s="6" t="inlineStr">
+      <c r="D135" s="6" t="inlineStr">
         <is>
           <t>GMP-101-230065</t>
         </is>
       </c>
-      <c r="E133" s="7" t="inlineStr">
+      <c r="E135" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 VHF CAMİ ALICI</t>
         </is>
       </c>
-      <c r="F133" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G133" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H133" s="9" t="n">
+      <c r="F135" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H135" s="9" t="n">
         <v>5433.095</v>
       </c>
-      <c r="I133" s="10" t="n">
+      <c r="I135" s="10" t="n">
         <v>5433.1</v>
       </c>
-      <c r="J133" s="6" t="n"/>
-      <c r="K133" s="6" t="n"/>
-      <c r="L133" s="6" t="n"/>
-    </row>
-    <row r="134" ht="20" customHeight="1">
-      <c r="A134" s="11" t="inlineStr">
+      <c r="J135" s="6" t="n"/>
+      <c r="K135" s="6" t="n"/>
+      <c r="L135" s="6" t="n"/>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B134" s="11" t="inlineStr">
+      <c r="B136" s="11" t="inlineStr">
         <is>
           <t>MMGMIR61003</t>
         </is>
       </c>
-      <c r="C134" s="12" t="inlineStr">
+      <c r="C136" s="12" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 VHF CAMİİ ALICI</t>
         </is>
       </c>
-      <c r="D134" s="11" t="n"/>
-      <c r="E134" s="11" t="n"/>
-      <c r="F134" s="11" t="n"/>
-      <c r="G134" s="11" t="n"/>
-      <c r="H134" s="11" t="n"/>
-      <c r="I134" s="11" t="n"/>
-      <c r="J134" s="13" t="n">
+      <c r="D136" s="11" t="n"/>
+      <c r="E136" s="11" t="n"/>
+      <c r="F136" s="11" t="n"/>
+      <c r="G136" s="11" t="n"/>
+      <c r="H136" s="11" t="n"/>
+      <c r="I136" s="11" t="n"/>
+      <c r="J136" s="13" t="n">
         <v>5433.1</v>
       </c>
-      <c r="K134" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L134" s="13" t="n">
+      <c r="K136" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" s="13" t="n">
         <v>5433.1</v>
       </c>
     </row>
-    <row r="135" ht="6" customHeight="1"/>
-    <row r="136" ht="22" customHeight="1">
-      <c r="A136" s="3" t="inlineStr">
+    <row r="137" ht="6" customHeight="1"/>
+    <row r="138" ht="22" customHeight="1">
+      <c r="A138" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B136" s="3" t="inlineStr">
+      <c r="B138" s="3" t="inlineStr">
         <is>
           <t>MMGMIR61017</t>
         </is>
       </c>
-      <c r="C136" s="4" t="inlineStr">
+      <c r="C138" s="4" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 UHF CAMİ ALICI (AMFİSİZ)</t>
         </is>
       </c>
-      <c r="D136" s="3" t="n"/>
-      <c r="E136" s="3" t="n"/>
-      <c r="F136" s="3" t="n"/>
-      <c r="G136" s="3" t="n"/>
-      <c r="H136" s="3" t="n"/>
-      <c r="I136" s="3" t="n"/>
-      <c r="J136" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" ht="18" customHeight="1">
-      <c r="A137" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B137" s="6" t="inlineStr">
+      <c r="D138" s="3" t="n"/>
+      <c r="E138" s="3" t="n"/>
+      <c r="F138" s="3" t="n"/>
+      <c r="G138" s="3" t="n"/>
+      <c r="H138" s="3" t="n"/>
+      <c r="I138" s="3" t="n"/>
+      <c r="J138" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" ht="18" customHeight="1">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
         <is>
           <t>MMGMIR61017</t>
         </is>
       </c>
-      <c r="C137" s="7" t="inlineStr">
+      <c r="C139" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 UHF CAMİ ALICI (AMFİSİZ)</t>
         </is>
       </c>
-      <c r="D137" s="6" t="inlineStr">
+      <c r="D139" s="6" t="inlineStr">
         <is>
           <t>GMP-101-230079</t>
         </is>
       </c>
-      <c r="E137" s="7" t="inlineStr">
+      <c r="E139" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 UHF CAMİ ALICI (AMFİSİZ)</t>
         </is>
       </c>
-      <c r="F137" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G137" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H137" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I137" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J137" s="6" t="n"/>
-      <c r="K137" s="6" t="n"/>
-      <c r="L137" s="6" t="n"/>
-    </row>
-    <row r="138" ht="20" customHeight="1">
-      <c r="A138" s="11" t="inlineStr">
+      <c r="F139" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H139" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="6" t="n"/>
+      <c r="K139" s="6" t="n"/>
+      <c r="L139" s="6" t="n"/>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B138" s="11" t="inlineStr">
+      <c r="B140" s="11" t="inlineStr">
         <is>
           <t>MMGMIR61017</t>
         </is>
       </c>
-      <c r="C138" s="12" t="inlineStr">
+      <c r="C140" s="12" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 UHF CAMİ ALICI (AMFİSİZ)</t>
         </is>
       </c>
-      <c r="D138" s="11" t="n"/>
-      <c r="E138" s="11" t="n"/>
-      <c r="F138" s="11" t="n"/>
-      <c r="G138" s="11" t="n"/>
-      <c r="H138" s="11" t="n"/>
-      <c r="I138" s="11" t="n"/>
-      <c r="J138" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" ht="6" customHeight="1"/>
-    <row r="140" ht="22" customHeight="1">
-      <c r="A140" s="3" t="inlineStr">
+      <c r="D140" s="11" t="n"/>
+      <c r="E140" s="11" t="n"/>
+      <c r="F140" s="11" t="n"/>
+      <c r="G140" s="11" t="n"/>
+      <c r="H140" s="11" t="n"/>
+      <c r="I140" s="11" t="n"/>
+      <c r="J140" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" ht="6" customHeight="1"/>
+    <row r="142" ht="22" customHeight="1">
+      <c r="A142" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B140" s="3" t="inlineStr">
+      <c r="B142" s="3" t="inlineStr">
         <is>
           <t>MMGMIR61020</t>
         </is>
       </c>
-      <c r="C140" s="4" t="inlineStr">
+      <c r="C142" s="4" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 ANONS ALICI (TELSİZSİZ)</t>
         </is>
       </c>
-      <c r="D140" s="3" t="n"/>
-      <c r="E140" s="3" t="n"/>
-      <c r="F140" s="3" t="n"/>
-      <c r="G140" s="3" t="n"/>
-      <c r="H140" s="3" t="n"/>
-      <c r="I140" s="3" t="n"/>
-      <c r="J140" s="5" t="n">
+      <c r="D142" s="3" t="n"/>
+      <c r="E142" s="3" t="n"/>
+      <c r="F142" s="3" t="n"/>
+      <c r="G142" s="3" t="n"/>
+      <c r="H142" s="3" t="n"/>
+      <c r="I142" s="3" t="n"/>
+      <c r="J142" s="5" t="n">
         <v>2509.51</v>
       </c>
-      <c r="K140" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L140" s="5" t="n">
+      <c r="K142" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" s="5" t="n">
         <v>2509.51</v>
       </c>
     </row>
-    <row r="141" ht="18" customHeight="1">
-      <c r="A141" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B141" s="6" t="inlineStr">
+    <row r="143" ht="18" customHeight="1">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
         <is>
           <t>MMGMIR61020</t>
         </is>
       </c>
-      <c r="C141" s="7" t="inlineStr">
+      <c r="C143" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 ANONS ALICI (TELSİZSİZ)</t>
         </is>
       </c>
-      <c r="D141" s="6" t="inlineStr">
+      <c r="D143" s="6" t="inlineStr">
         <is>
           <t>GMP-101-230082</t>
         </is>
       </c>
-      <c r="E141" s="7" t="inlineStr">
+      <c r="E143" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 ANONS ALICI (TELSİZSİZ)</t>
         </is>
       </c>
-      <c r="F141" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G141" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H141" s="9" t="n">
+      <c r="F143" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H143" s="9" t="n">
         <v>2509.5097</v>
       </c>
-      <c r="I141" s="10" t="n">
+      <c r="I143" s="10" t="n">
         <v>2509.51</v>
       </c>
-      <c r="J141" s="6" t="n"/>
-      <c r="K141" s="6" t="n"/>
-      <c r="L141" s="6" t="n"/>
-    </row>
-    <row r="142" ht="20" customHeight="1">
-      <c r="A142" s="11" t="inlineStr">
+      <c r="J143" s="6" t="n"/>
+      <c r="K143" s="6" t="n"/>
+      <c r="L143" s="6" t="n"/>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B142" s="11" t="inlineStr">
+      <c r="B144" s="11" t="inlineStr">
         <is>
           <t>MMGMIR61020</t>
         </is>
       </c>
-      <c r="C142" s="12" t="inlineStr">
+      <c r="C144" s="12" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 ANONS ALICI (TELSİZSİZ)</t>
         </is>
       </c>
-      <c r="D142" s="11" t="n"/>
-      <c r="E142" s="11" t="n"/>
-      <c r="F142" s="11" t="n"/>
-      <c r="G142" s="11" t="n"/>
-      <c r="H142" s="11" t="n"/>
-      <c r="I142" s="11" t="n"/>
-      <c r="J142" s="13" t="n">
+      <c r="D144" s="11" t="n"/>
+      <c r="E144" s="11" t="n"/>
+      <c r="F144" s="11" t="n"/>
+      <c r="G144" s="11" t="n"/>
+      <c r="H144" s="11" t="n"/>
+      <c r="I144" s="11" t="n"/>
+      <c r="J144" s="13" t="n">
         <v>2509.51</v>
       </c>
-      <c r="K142" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L142" s="13" t="n">
+      <c r="K144" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" s="13" t="n">
         <v>2509.51</v>
       </c>
     </row>
-    <row r="143" ht="6" customHeight="1"/>
-    <row r="144" ht="22" customHeight="1">
-      <c r="A144" s="3" t="inlineStr">
+    <row r="145" ht="6" customHeight="1"/>
+    <row r="146" ht="22" customHeight="1">
+      <c r="A146" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B144" s="3" t="inlineStr">
+      <c r="B146" s="3" t="inlineStr">
         <is>
           <t>MMGMIR61021</t>
         </is>
       </c>
-      <c r="C144" s="4" t="inlineStr">
+      <c r="C146" s="4" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 VHF AKÜ BESLEMELİ ALICI</t>
         </is>
       </c>
-      <c r="D144" s="3" t="n"/>
-      <c r="E144" s="3" t="n"/>
-      <c r="F144" s="3" t="n"/>
-      <c r="G144" s="3" t="n"/>
-      <c r="H144" s="3" t="n"/>
-      <c r="I144" s="3" t="n"/>
-      <c r="J144" s="5" t="n">
+      <c r="D146" s="3" t="n"/>
+      <c r="E146" s="3" t="n"/>
+      <c r="F146" s="3" t="n"/>
+      <c r="G146" s="3" t="n"/>
+      <c r="H146" s="3" t="n"/>
+      <c r="I146" s="3" t="n"/>
+      <c r="J146" s="5" t="n">
         <v>2650.21</v>
       </c>
-      <c r="K144" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L144" s="5" t="n">
+      <c r="K146" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" s="5" t="n">
         <v>2650.21</v>
       </c>
     </row>
-    <row r="145" ht="18" customHeight="1">
-      <c r="A145" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B145" s="6" t="inlineStr">
+    <row r="147" ht="18" customHeight="1">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
         <is>
           <t>MMGMIR61021</t>
         </is>
       </c>
-      <c r="C145" s="7" t="inlineStr">
+      <c r="C147" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 VHF AKÜ BESLEMELİ ALICI</t>
         </is>
       </c>
-      <c r="D145" s="6" t="inlineStr">
+      <c r="D147" s="6" t="inlineStr">
         <is>
           <t>GMP-101-230083</t>
         </is>
       </c>
-      <c r="E145" s="7" t="inlineStr">
+      <c r="E147" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 VHF AKÜ BESLEMELİ ALICI</t>
         </is>
       </c>
-      <c r="F145" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G145" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H145" s="9" t="n">
+      <c r="F147" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H147" s="9" t="n">
         <v>2650.209</v>
       </c>
-      <c r="I145" s="10" t="n">
+      <c r="I147" s="10" t="n">
         <v>2650.21</v>
       </c>
-      <c r="J145" s="6" t="n"/>
-      <c r="K145" s="6" t="n"/>
-      <c r="L145" s="6" t="n"/>
-    </row>
-    <row r="146" ht="20" customHeight="1">
-      <c r="A146" s="11" t="inlineStr">
+      <c r="J147" s="6" t="n"/>
+      <c r="K147" s="6" t="n"/>
+      <c r="L147" s="6" t="n"/>
+    </row>
+    <row r="148" ht="20" customHeight="1">
+      <c r="A148" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B146" s="11" t="inlineStr">
+      <c r="B148" s="11" t="inlineStr">
         <is>
           <t>MMGMIR61021</t>
         </is>
       </c>
-      <c r="C146" s="12" t="inlineStr">
+      <c r="C148" s="12" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 VHF AKÜ BESLEMELİ ALICI</t>
         </is>
       </c>
-      <c r="D146" s="11" t="n"/>
-      <c r="E146" s="11" t="n"/>
-      <c r="F146" s="11" t="n"/>
-      <c r="G146" s="11" t="n"/>
-      <c r="H146" s="11" t="n"/>
-      <c r="I146" s="11" t="n"/>
-      <c r="J146" s="13" t="n">
+      <c r="D148" s="11" t="n"/>
+      <c r="E148" s="11" t="n"/>
+      <c r="F148" s="11" t="n"/>
+      <c r="G148" s="11" t="n"/>
+      <c r="H148" s="11" t="n"/>
+      <c r="I148" s="11" t="n"/>
+      <c r="J148" s="13" t="n">
         <v>2650.21</v>
       </c>
-      <c r="K146" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L146" s="13" t="n">
+      <c r="K148" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" s="13" t="n">
         <v>2650.21</v>
       </c>
     </row>
-    <row r="147" ht="6" customHeight="1"/>
-    <row r="148" ht="22" customHeight="1">
-      <c r="A148" s="3" t="inlineStr">
+    <row r="149" ht="6" customHeight="1"/>
+    <row r="150" ht="22" customHeight="1">
+      <c r="A150" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B148" s="3" t="inlineStr">
+      <c r="B150" s="3" t="inlineStr">
         <is>
           <t>MMGMIR61022</t>
         </is>
       </c>
-      <c r="C148" s="4" t="inlineStr">
+      <c r="C150" s="4" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 UHF AKÜ BESLEMELİ ALICI</t>
         </is>
       </c>
-      <c r="D148" s="3" t="n"/>
-      <c r="E148" s="3" t="n"/>
-      <c r="F148" s="3" t="n"/>
-      <c r="G148" s="3" t="n"/>
-      <c r="H148" s="3" t="n"/>
-      <c r="I148" s="3" t="n"/>
-      <c r="J148" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K148" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L148" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" ht="18" customHeight="1">
-      <c r="A149" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B149" s="6" t="inlineStr">
+      <c r="D150" s="3" t="n"/>
+      <c r="E150" s="3" t="n"/>
+      <c r="F150" s="3" t="n"/>
+      <c r="G150" s="3" t="n"/>
+      <c r="H150" s="3" t="n"/>
+      <c r="I150" s="3" t="n"/>
+      <c r="J150" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" ht="18" customHeight="1">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B151" s="6" t="inlineStr">
         <is>
           <t>MMGMIR61022</t>
         </is>
       </c>
-      <c r="C149" s="7" t="inlineStr">
+      <c r="C151" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 UHF AKÜ BESLEMELİ ALICI</t>
         </is>
       </c>
-      <c r="D149" s="6" t="inlineStr">
+      <c r="D151" s="6" t="inlineStr">
         <is>
           <t>GMP-101-230084</t>
         </is>
       </c>
-      <c r="E149" s="7" t="inlineStr">
+      <c r="E151" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 UHF AKÜ BESLEMELİ ALICI</t>
         </is>
       </c>
-      <c r="F149" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G149" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H149" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I149" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J149" s="6" t="n"/>
-      <c r="K149" s="6" t="n"/>
-      <c r="L149" s="6" t="n"/>
-    </row>
-    <row r="150" ht="20" customHeight="1">
-      <c r="A150" s="11" t="inlineStr">
+      <c r="F151" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H151" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" s="6" t="n"/>
+      <c r="K151" s="6" t="n"/>
+      <c r="L151" s="6" t="n"/>
+    </row>
+    <row r="152" ht="20" customHeight="1">
+      <c r="A152" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B150" s="11" t="inlineStr">
+      <c r="B152" s="11" t="inlineStr">
         <is>
           <t>MMGMIR61022</t>
         </is>
       </c>
-      <c r="C150" s="12" t="inlineStr">
+      <c r="C152" s="12" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 UHF AKÜ BESLEMELİ ALICI</t>
         </is>
       </c>
-      <c r="D150" s="11" t="n"/>
-      <c r="E150" s="11" t="n"/>
-      <c r="F150" s="11" t="n"/>
-      <c r="G150" s="11" t="n"/>
-      <c r="H150" s="11" t="n"/>
-      <c r="I150" s="11" t="n"/>
-      <c r="J150" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K150" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L150" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" ht="6" customHeight="1"/>
-    <row r="152" ht="22" customHeight="1">
-      <c r="A152" s="3" t="inlineStr">
+      <c r="D152" s="11" t="n"/>
+      <c r="E152" s="11" t="n"/>
+      <c r="F152" s="11" t="n"/>
+      <c r="G152" s="11" t="n"/>
+      <c r="H152" s="11" t="n"/>
+      <c r="I152" s="11" t="n"/>
+      <c r="J152" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" ht="6" customHeight="1"/>
+    <row r="154" ht="22" customHeight="1">
+      <c r="A154" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B152" s="3" t="inlineStr">
+      <c r="B154" s="3" t="inlineStr">
         <is>
           <t>MMGMIR61023</t>
         </is>
       </c>
-      <c r="C152" s="4" t="inlineStr">
+      <c r="C154" s="4" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 B UHF ALICI</t>
         </is>
       </c>
-      <c r="D152" s="3" t="n"/>
-      <c r="E152" s="3" t="n"/>
-      <c r="F152" s="3" t="n"/>
-      <c r="G152" s="3" t="n"/>
-      <c r="H152" s="3" t="n"/>
-      <c r="I152" s="3" t="n"/>
-      <c r="J152" s="5" t="n">
+      <c r="D154" s="3" t="n"/>
+      <c r="E154" s="3" t="n"/>
+      <c r="F154" s="3" t="n"/>
+      <c r="G154" s="3" t="n"/>
+      <c r="H154" s="3" t="n"/>
+      <c r="I154" s="3" t="n"/>
+      <c r="J154" s="5" t="n">
         <v>2649.56</v>
       </c>
-      <c r="K152" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L152" s="5" t="n">
+      <c r="K154" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" s="5" t="n">
         <v>2649.56</v>
       </c>
     </row>
-    <row r="153" ht="18" customHeight="1">
-      <c r="A153" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B153" s="6" t="inlineStr">
+    <row r="155" ht="18" customHeight="1">
+      <c r="A155" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B155" s="6" t="inlineStr">
         <is>
           <t>MMGMIR61023</t>
         </is>
       </c>
-      <c r="C153" s="7" t="inlineStr">
+      <c r="C155" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 B UHF ALICI</t>
         </is>
       </c>
-      <c r="D153" s="6" t="inlineStr">
+      <c r="D155" s="6" t="inlineStr">
         <is>
           <t>GMP-101-230085</t>
         </is>
       </c>
-      <c r="E153" s="7" t="inlineStr">
+      <c r="E155" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 B UHF ALICI</t>
         </is>
       </c>
-      <c r="F153" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G153" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H153" s="9" t="n">
+      <c r="F155" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G155" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H155" s="9" t="n">
         <v>2649.5622</v>
       </c>
-      <c r="I153" s="10" t="n">
+      <c r="I155" s="10" t="n">
         <v>2649.56</v>
       </c>
-      <c r="J153" s="6" t="n"/>
-      <c r="K153" s="6" t="n"/>
-      <c r="L153" s="6" t="n"/>
-    </row>
-    <row r="154" ht="20" customHeight="1">
-      <c r="A154" s="11" t="inlineStr">
+      <c r="J155" s="6" t="n"/>
+      <c r="K155" s="6" t="n"/>
+      <c r="L155" s="6" t="n"/>
+    </row>
+    <row r="156" ht="20" customHeight="1">
+      <c r="A156" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B154" s="11" t="inlineStr">
+      <c r="B156" s="11" t="inlineStr">
         <is>
           <t>MMGMIR61023</t>
         </is>
       </c>
-      <c r="C154" s="12" t="inlineStr">
+      <c r="C156" s="12" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 B UHF ALICI</t>
         </is>
       </c>
-      <c r="D154" s="11" t="n"/>
-      <c r="E154" s="11" t="n"/>
-      <c r="F154" s="11" t="n"/>
-      <c r="G154" s="11" t="n"/>
-      <c r="H154" s="11" t="n"/>
-      <c r="I154" s="11" t="n"/>
-      <c r="J154" s="13" t="n">
+      <c r="D156" s="11" t="n"/>
+      <c r="E156" s="11" t="n"/>
+      <c r="F156" s="11" t="n"/>
+      <c r="G156" s="11" t="n"/>
+      <c r="H156" s="11" t="n"/>
+      <c r="I156" s="11" t="n"/>
+      <c r="J156" s="13" t="n">
         <v>2649.56</v>
       </c>
-      <c r="K154" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L154" s="13" t="n">
+      <c r="K156" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" s="13" t="n">
         <v>2649.56</v>
       </c>
     </row>
-    <row r="155" ht="6" customHeight="1"/>
-    <row r="156" ht="22" customHeight="1">
-      <c r="A156" s="3" t="inlineStr">
+    <row r="157" ht="6" customHeight="1"/>
+    <row r="158" ht="22" customHeight="1">
+      <c r="A158" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B156" s="3" t="inlineStr">
+      <c r="B158" s="3" t="inlineStr">
         <is>
           <t>MMGMIR61028</t>
         </is>
       </c>
-      <c r="C156" s="4" t="inlineStr">
+      <c r="C158" s="4" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 BAP VHF ALICI</t>
         </is>
       </c>
-      <c r="D156" s="3" t="n"/>
-      <c r="E156" s="3" t="n"/>
-      <c r="F156" s="3" t="n"/>
-      <c r="G156" s="3" t="n"/>
-      <c r="H156" s="3" t="n"/>
-      <c r="I156" s="3" t="n"/>
-      <c r="J156" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K156" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L156" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" ht="18" customHeight="1">
-      <c r="A157" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B157" s="6" t="inlineStr">
+      <c r="D158" s="3" t="n"/>
+      <c r="E158" s="3" t="n"/>
+      <c r="F158" s="3" t="n"/>
+      <c r="G158" s="3" t="n"/>
+      <c r="H158" s="3" t="n"/>
+      <c r="I158" s="3" t="n"/>
+      <c r="J158" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" ht="18" customHeight="1">
+      <c r="A159" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B159" s="6" t="inlineStr">
         <is>
           <t>MMGMIR61028</t>
         </is>
       </c>
-      <c r="C157" s="7" t="inlineStr">
+      <c r="C159" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 BAP VHF ALICI</t>
         </is>
       </c>
-      <c r="D157" s="6" t="inlineStr">
+      <c r="D159" s="6" t="inlineStr">
         <is>
           <t>GMP-101-230090</t>
         </is>
       </c>
-      <c r="E157" s="7" t="inlineStr">
+      <c r="E159" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 BAP VHF ALICI</t>
         </is>
       </c>
-      <c r="F157" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G157" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H157" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I157" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J157" s="6" t="n"/>
-      <c r="K157" s="6" t="n"/>
-      <c r="L157" s="6" t="n"/>
-    </row>
-    <row r="158" ht="20" customHeight="1">
-      <c r="A158" s="11" t="inlineStr">
+      <c r="F159" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H159" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" s="6" t="n"/>
+      <c r="K159" s="6" t="n"/>
+      <c r="L159" s="6" t="n"/>
+    </row>
+    <row r="160" ht="20" customHeight="1">
+      <c r="A160" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B158" s="11" t="inlineStr">
+      <c r="B160" s="11" t="inlineStr">
         <is>
           <t>MMGMIR61028</t>
         </is>
       </c>
-      <c r="C158" s="12" t="inlineStr">
+      <c r="C160" s="12" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 BAP VHF ALICI</t>
         </is>
       </c>
-      <c r="D158" s="11" t="n"/>
-      <c r="E158" s="11" t="n"/>
-      <c r="F158" s="11" t="n"/>
-      <c r="G158" s="11" t="n"/>
-      <c r="H158" s="11" t="n"/>
-      <c r="I158" s="11" t="n"/>
-      <c r="J158" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K158" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L158" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" ht="6" customHeight="1"/>
-    <row r="160" ht="22" customHeight="1">
-      <c r="A160" s="3" t="inlineStr">
+      <c r="D160" s="11" t="n"/>
+      <c r="E160" s="11" t="n"/>
+      <c r="F160" s="11" t="n"/>
+      <c r="G160" s="11" t="n"/>
+      <c r="H160" s="11" t="n"/>
+      <c r="I160" s="11" t="n"/>
+      <c r="J160" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" ht="6" customHeight="1"/>
+    <row r="162" ht="22" customHeight="1">
+      <c r="A162" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B160" s="3" t="inlineStr">
+      <c r="B162" s="3" t="inlineStr">
         <is>
           <t>MMGMIR61030</t>
         </is>
       </c>
-      <c r="C160" s="4" t="inlineStr">
+      <c r="C162" s="4" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 VHF AKÜLÜ GÜNEŞ PANELLİ ALICI</t>
         </is>
       </c>
-      <c r="D160" s="3" t="n"/>
-      <c r="E160" s="3" t="n"/>
-      <c r="F160" s="3" t="n"/>
-      <c r="G160" s="3" t="n"/>
-      <c r="H160" s="3" t="n"/>
-      <c r="I160" s="3" t="n"/>
-      <c r="J160" s="5" t="n">
+      <c r="D162" s="3" t="n"/>
+      <c r="E162" s="3" t="n"/>
+      <c r="F162" s="3" t="n"/>
+      <c r="G162" s="3" t="n"/>
+      <c r="H162" s="3" t="n"/>
+      <c r="I162" s="3" t="n"/>
+      <c r="J162" s="5" t="n">
         <v>5668.24</v>
       </c>
-      <c r="K160" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L160" s="5" t="n">
+      <c r="K162" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" s="5" t="n">
         <v>5668.24</v>
       </c>
     </row>
-    <row r="161" ht="18" customHeight="1">
-      <c r="A161" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B161" s="6" t="inlineStr">
+    <row r="163" ht="18" customHeight="1">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
         <is>
           <t>MMGMIR61030</t>
         </is>
       </c>
-      <c r="C161" s="7" t="inlineStr">
+      <c r="C163" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 VHF AKÜLÜ GÜNEŞ PANELLİ ALICI</t>
         </is>
       </c>
-      <c r="D161" s="6" t="inlineStr">
+      <c r="D163" s="6" t="inlineStr">
         <is>
           <t>GMP-101-230092</t>
         </is>
       </c>
-      <c r="E161" s="7" t="inlineStr">
+      <c r="E163" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 VHF AKÜLÜ GÜNEŞ PANELLİ ALICI</t>
         </is>
       </c>
-      <c r="F161" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G161" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H161" s="9" t="n">
+      <c r="F163" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G163" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H163" s="9" t="n">
         <v>5668.24</v>
       </c>
-      <c r="I161" s="10" t="n">
+      <c r="I163" s="10" t="n">
         <v>5668.24</v>
       </c>
-      <c r="J161" s="6" t="n"/>
-      <c r="K161" s="6" t="n"/>
-      <c r="L161" s="6" t="n"/>
-    </row>
-    <row r="162" ht="20" customHeight="1">
-      <c r="A162" s="11" t="inlineStr">
+      <c r="J163" s="6" t="n"/>
+      <c r="K163" s="6" t="n"/>
+      <c r="L163" s="6" t="n"/>
+    </row>
+    <row r="164" ht="20" customHeight="1">
+      <c r="A164" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B162" s="11" t="inlineStr">
+      <c r="B164" s="11" t="inlineStr">
         <is>
           <t>MMGMIR61030</t>
         </is>
       </c>
-      <c r="C162" s="12" t="inlineStr">
+      <c r="C164" s="12" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 VHF AKÜLÜ GÜNEŞ PANELLİ ALICI</t>
         </is>
       </c>
-      <c r="D162" s="11" t="n"/>
-      <c r="E162" s="11" t="n"/>
-      <c r="F162" s="11" t="n"/>
-      <c r="G162" s="11" t="n"/>
-      <c r="H162" s="11" t="n"/>
-      <c r="I162" s="11" t="n"/>
-      <c r="J162" s="13" t="n">
+      <c r="D164" s="11" t="n"/>
+      <c r="E164" s="11" t="n"/>
+      <c r="F164" s="11" t="n"/>
+      <c r="G164" s="11" t="n"/>
+      <c r="H164" s="11" t="n"/>
+      <c r="I164" s="11" t="n"/>
+      <c r="J164" s="13" t="n">
         <v>5668.24</v>
       </c>
-      <c r="K162" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L162" s="13" t="n">
+      <c r="K164" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" s="13" t="n">
         <v>5668.24</v>
       </c>
     </row>
-    <row r="163" ht="6" customHeight="1"/>
-    <row r="164" ht="22" customHeight="1">
-      <c r="A164" s="3" t="inlineStr">
+    <row r="165" ht="6" customHeight="1"/>
+    <row r="166" ht="22" customHeight="1">
+      <c r="A166" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B164" s="3" t="inlineStr">
+      <c r="B166" s="3" t="inlineStr">
         <is>
           <t>MMGMIR61031</t>
         </is>
       </c>
-      <c r="C164" s="4" t="inlineStr">
+      <c r="C166" s="4" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 B ANONS ALICI-TELSİZSİZ</t>
         </is>
       </c>
-      <c r="D164" s="3" t="n"/>
-      <c r="E164" s="3" t="n"/>
-      <c r="F164" s="3" t="n"/>
-      <c r="G164" s="3" t="n"/>
-      <c r="H164" s="3" t="n"/>
-      <c r="I164" s="3" t="n"/>
-      <c r="J164" s="5" t="n">
+      <c r="D166" s="3" t="n"/>
+      <c r="E166" s="3" t="n"/>
+      <c r="F166" s="3" t="n"/>
+      <c r="G166" s="3" t="n"/>
+      <c r="H166" s="3" t="n"/>
+      <c r="I166" s="3" t="n"/>
+      <c r="J166" s="5" t="n">
         <v>4111.13</v>
       </c>
-      <c r="K164" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L164" s="5" t="n">
+      <c r="K166" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" s="5" t="n">
         <v>4111.13</v>
       </c>
     </row>
-    <row r="165" ht="18" customHeight="1">
-      <c r="A165" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B165" s="6" t="inlineStr">
+    <row r="167" ht="18" customHeight="1">
+      <c r="A167" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B167" s="6" t="inlineStr">
         <is>
           <t>MMGMIR61031</t>
         </is>
       </c>
-      <c r="C165" s="7" t="inlineStr">
+      <c r="C167" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 B ANONS ALICI-TELSİZSİZ</t>
         </is>
       </c>
-      <c r="D165" s="6" t="inlineStr">
+      <c r="D167" s="6" t="inlineStr">
         <is>
           <t>GMP-101-230086</t>
         </is>
       </c>
-      <c r="E165" s="7" t="inlineStr">
+      <c r="E167" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 B VHF ALICI</t>
         </is>
       </c>
-      <c r="F165" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G165" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H165" s="9" t="n">
+      <c r="F167" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G167" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H167" s="9" t="n">
         <v>4111.1265</v>
       </c>
-      <c r="I165" s="10" t="n">
+      <c r="I167" s="10" t="n">
         <v>4111.13</v>
       </c>
-      <c r="J165" s="6" t="n"/>
-      <c r="K165" s="6" t="n"/>
-      <c r="L165" s="6" t="n"/>
-    </row>
-    <row r="166" ht="20" customHeight="1">
-      <c r="A166" s="11" t="inlineStr">
+      <c r="J167" s="6" t="n"/>
+      <c r="K167" s="6" t="n"/>
+      <c r="L167" s="6" t="n"/>
+    </row>
+    <row r="168" ht="20" customHeight="1">
+      <c r="A168" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B166" s="11" t="inlineStr">
+      <c r="B168" s="11" t="inlineStr">
         <is>
           <t>MMGMIR61031</t>
         </is>
       </c>
-      <c r="C166" s="12" t="inlineStr">
+      <c r="C168" s="12" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 B ANONS ALICI-TELSİZSİZ</t>
         </is>
       </c>
-      <c r="D166" s="11" t="n"/>
-      <c r="E166" s="11" t="n"/>
-      <c r="F166" s="11" t="n"/>
-      <c r="G166" s="11" t="n"/>
-      <c r="H166" s="11" t="n"/>
-      <c r="I166" s="11" t="n"/>
-      <c r="J166" s="13" t="n">
+      <c r="D168" s="11" t="n"/>
+      <c r="E168" s="11" t="n"/>
+      <c r="F168" s="11" t="n"/>
+      <c r="G168" s="11" t="n"/>
+      <c r="H168" s="11" t="n"/>
+      <c r="I168" s="11" t="n"/>
+      <c r="J168" s="13" t="n">
         <v>4111.13</v>
       </c>
-      <c r="K166" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L166" s="13" t="n">
+      <c r="K168" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" s="13" t="n">
         <v>4111.13</v>
       </c>
     </row>
-    <row r="167" ht="6" customHeight="1"/>
-    <row r="168" ht="22" customHeight="1">
-      <c r="A168" s="3" t="inlineStr">
+    <row r="169" ht="6" customHeight="1"/>
+    <row r="170" ht="22" customHeight="1">
+      <c r="A170" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B168" s="3" t="inlineStr">
+      <c r="B170" s="3" t="inlineStr">
         <is>
           <t>MMGMIR61032</t>
         </is>
       </c>
-      <c r="C168" s="4" t="inlineStr">
+      <c r="C170" s="4" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 B VHF AKÜ BESLEMELİ ALICI</t>
         </is>
       </c>
-      <c r="D168" s="3" t="n"/>
-      <c r="E168" s="3" t="n"/>
-      <c r="F168" s="3" t="n"/>
-      <c r="G168" s="3" t="n"/>
-      <c r="H168" s="3" t="n"/>
-      <c r="I168" s="3" t="n"/>
-      <c r="J168" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K168" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L168" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" ht="18" customHeight="1">
-      <c r="A169" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B169" s="6" t="inlineStr">
+      <c r="D170" s="3" t="n"/>
+      <c r="E170" s="3" t="n"/>
+      <c r="F170" s="3" t="n"/>
+      <c r="G170" s="3" t="n"/>
+      <c r="H170" s="3" t="n"/>
+      <c r="I170" s="3" t="n"/>
+      <c r="J170" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L170" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" ht="18" customHeight="1">
+      <c r="A171" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B171" s="6" t="inlineStr">
         <is>
           <t>MMGMIR61032</t>
         </is>
       </c>
-      <c r="C169" s="7" t="inlineStr">
+      <c r="C171" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 B VHF AKÜ BESLEMELİ ALICI</t>
         </is>
       </c>
-      <c r="D169" s="6" t="inlineStr">
+      <c r="D171" s="6" t="inlineStr">
         <is>
           <t>GMP-101-230094</t>
         </is>
       </c>
-      <c r="E169" s="7" t="inlineStr">
+      <c r="E171" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 B VHF AKÜ BESLEMELİ ALICI</t>
         </is>
       </c>
-      <c r="F169" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G169" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H169" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I169" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J169" s="6" t="n"/>
-      <c r="K169" s="6" t="n"/>
-      <c r="L169" s="6" t="n"/>
-    </row>
-    <row r="170" ht="20" customHeight="1">
-      <c r="A170" s="11" t="inlineStr">
+      <c r="F171" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G171" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H171" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I171" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" s="6" t="n"/>
+      <c r="K171" s="6" t="n"/>
+      <c r="L171" s="6" t="n"/>
+    </row>
+    <row r="172" ht="20" customHeight="1">
+      <c r="A172" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B170" s="11" t="inlineStr">
+      <c r="B172" s="11" t="inlineStr">
         <is>
           <t>MMGMIR61032</t>
         </is>
       </c>
-      <c r="C170" s="12" t="inlineStr">
+      <c r="C172" s="12" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 B VHF AKÜ BESLEMELİ ALICI</t>
         </is>
       </c>
-      <c r="D170" s="11" t="n"/>
-      <c r="E170" s="11" t="n"/>
-      <c r="F170" s="11" t="n"/>
-      <c r="G170" s="11" t="n"/>
-      <c r="H170" s="11" t="n"/>
-      <c r="I170" s="11" t="n"/>
-      <c r="J170" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K170" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L170" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" ht="6" customHeight="1"/>
-    <row r="172" ht="22" customHeight="1">
-      <c r="A172" s="3" t="inlineStr">
+      <c r="D172" s="11" t="n"/>
+      <c r="E172" s="11" t="n"/>
+      <c r="F172" s="11" t="n"/>
+      <c r="G172" s="11" t="n"/>
+      <c r="H172" s="11" t="n"/>
+      <c r="I172" s="11" t="n"/>
+      <c r="J172" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L172" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" ht="6" customHeight="1"/>
+    <row r="174" ht="22" customHeight="1">
+      <c r="A174" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B172" s="3" t="inlineStr">
+      <c r="B174" s="3" t="inlineStr">
         <is>
           <t>MMGMIR61033</t>
         </is>
       </c>
-      <c r="C172" s="4" t="inlineStr">
+      <c r="C174" s="4" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 B UHF AKÜ BESLEMELİ ALICI</t>
         </is>
       </c>
-      <c r="D172" s="3" t="n"/>
-      <c r="E172" s="3" t="n"/>
-      <c r="F172" s="3" t="n"/>
-      <c r="G172" s="3" t="n"/>
-      <c r="H172" s="3" t="n"/>
-      <c r="I172" s="3" t="n"/>
-      <c r="J172" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K172" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L172" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" ht="18" customHeight="1">
-      <c r="A173" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B173" s="6" t="inlineStr">
+      <c r="D174" s="3" t="n"/>
+      <c r="E174" s="3" t="n"/>
+      <c r="F174" s="3" t="n"/>
+      <c r="G174" s="3" t="n"/>
+      <c r="H174" s="3" t="n"/>
+      <c r="I174" s="3" t="n"/>
+      <c r="J174" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L174" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" ht="18" customHeight="1">
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B175" s="6" t="inlineStr">
         <is>
           <t>MMGMIR61033</t>
         </is>
       </c>
-      <c r="C173" s="7" t="inlineStr">
+      <c r="C175" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 B UHF AKÜ BESLEMELİ ALICI</t>
         </is>
       </c>
-      <c r="D173" s="6" t="inlineStr">
+      <c r="D175" s="6" t="inlineStr">
         <is>
           <t>GMP-101-230095</t>
         </is>
       </c>
-      <c r="E173" s="7" t="inlineStr">
+      <c r="E175" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 B UHF AKÜ BESLEMELİ ALICI</t>
         </is>
       </c>
-      <c r="F173" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G173" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H173" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I173" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J173" s="6" t="n"/>
-      <c r="K173" s="6" t="n"/>
-      <c r="L173" s="6" t="n"/>
-    </row>
-    <row r="174" ht="20" customHeight="1">
-      <c r="A174" s="11" t="inlineStr">
+      <c r="F175" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G175" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H175" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I175" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" s="6" t="n"/>
+      <c r="K175" s="6" t="n"/>
+      <c r="L175" s="6" t="n"/>
+    </row>
+    <row r="176" ht="20" customHeight="1">
+      <c r="A176" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B174" s="11" t="inlineStr">
+      <c r="B176" s="11" t="inlineStr">
         <is>
           <t>MMGMIR61033</t>
         </is>
       </c>
-      <c r="C174" s="12" t="inlineStr">
+      <c r="C176" s="12" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 B UHF AKÜ BESLEMELİ ALICI</t>
         </is>
       </c>
-      <c r="D174" s="11" t="n"/>
-      <c r="E174" s="11" t="n"/>
-      <c r="F174" s="11" t="n"/>
-      <c r="G174" s="11" t="n"/>
-      <c r="H174" s="11" t="n"/>
-      <c r="I174" s="11" t="n"/>
-      <c r="J174" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K174" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L174" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" ht="6" customHeight="1"/>
-    <row r="176" ht="22" customHeight="1">
-      <c r="A176" s="3" t="inlineStr">
+      <c r="D176" s="11" t="n"/>
+      <c r="E176" s="11" t="n"/>
+      <c r="F176" s="11" t="n"/>
+      <c r="G176" s="11" t="n"/>
+      <c r="H176" s="11" t="n"/>
+      <c r="I176" s="11" t="n"/>
+      <c r="J176" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L176" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" ht="6" customHeight="1"/>
+    <row r="178" ht="22" customHeight="1">
+      <c r="A178" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B176" s="3" t="inlineStr">
+      <c r="B178" s="3" t="inlineStr">
         <is>
           <t>MMGMIR61036</t>
         </is>
       </c>
-      <c r="C176" s="4" t="inlineStr">
+      <c r="C178" s="4" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 ESK VHF ALICI</t>
         </is>
       </c>
-      <c r="D176" s="3" t="n"/>
-      <c r="E176" s="3" t="n"/>
-      <c r="F176" s="3" t="n"/>
-      <c r="G176" s="3" t="n"/>
-      <c r="H176" s="3" t="n"/>
-      <c r="I176" s="3" t="n"/>
-      <c r="J176" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K176" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L176" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" ht="18" customHeight="1">
-      <c r="A177" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B177" s="6" t="inlineStr">
+      <c r="D178" s="3" t="n"/>
+      <c r="E178" s="3" t="n"/>
+      <c r="F178" s="3" t="n"/>
+      <c r="G178" s="3" t="n"/>
+      <c r="H178" s="3" t="n"/>
+      <c r="I178" s="3" t="n"/>
+      <c r="J178" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L178" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" ht="18" customHeight="1">
+      <c r="A179" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B179" s="6" t="inlineStr">
         <is>
           <t>MMGMIR61036</t>
         </is>
       </c>
-      <c r="C177" s="7" t="inlineStr">
+      <c r="C179" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 ESK VHF ALICI</t>
         </is>
       </c>
-      <c r="D177" s="6" t="inlineStr">
+      <c r="D179" s="6" t="inlineStr">
         <is>
           <t>GMP-101-230098</t>
         </is>
       </c>
-      <c r="E177" s="7" t="inlineStr">
+      <c r="E179" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 ESK VHF ALICI</t>
         </is>
       </c>
-      <c r="F177" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G177" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H177" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I177" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J177" s="6" t="n"/>
-      <c r="K177" s="6" t="n"/>
-      <c r="L177" s="6" t="n"/>
-    </row>
-    <row r="178" ht="20" customHeight="1">
-      <c r="A178" s="11" t="inlineStr">
+      <c r="F179" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G179" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H179" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I179" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" s="6" t="n"/>
+      <c r="K179" s="6" t="n"/>
+      <c r="L179" s="6" t="n"/>
+    </row>
+    <row r="180" ht="20" customHeight="1">
+      <c r="A180" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B178" s="11" t="inlineStr">
+      <c r="B180" s="11" t="inlineStr">
         <is>
           <t>MMGMIR61036</t>
         </is>
       </c>
-      <c r="C178" s="12" t="inlineStr">
+      <c r="C180" s="12" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 ESK VHF ALICI</t>
         </is>
       </c>
-      <c r="D178" s="11" t="n"/>
-      <c r="E178" s="11" t="n"/>
-      <c r="F178" s="11" t="n"/>
-      <c r="G178" s="11" t="n"/>
-      <c r="H178" s="11" t="n"/>
-      <c r="I178" s="11" t="n"/>
-      <c r="J178" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K178" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L178" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" ht="6" customHeight="1"/>
-    <row r="180" ht="22" customHeight="1">
-      <c r="A180" s="3" t="inlineStr">
+      <c r="D180" s="11" t="n"/>
+      <c r="E180" s="11" t="n"/>
+      <c r="F180" s="11" t="n"/>
+      <c r="G180" s="11" t="n"/>
+      <c r="H180" s="11" t="n"/>
+      <c r="I180" s="11" t="n"/>
+      <c r="J180" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L180" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" ht="6" customHeight="1"/>
+    <row r="182" ht="22" customHeight="1">
+      <c r="A182" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B180" s="3" t="inlineStr">
+      <c r="B182" s="3" t="inlineStr">
         <is>
           <t>MMGMIR61037</t>
         </is>
       </c>
-      <c r="C180" s="4" t="inlineStr">
+      <c r="C182" s="4" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 B UHF SORGULAMALI ALICI</t>
         </is>
       </c>
-      <c r="D180" s="3" t="n"/>
-      <c r="E180" s="3" t="n"/>
-      <c r="F180" s="3" t="n"/>
-      <c r="G180" s="3" t="n"/>
-      <c r="H180" s="3" t="n"/>
-      <c r="I180" s="3" t="n"/>
-      <c r="J180" s="5" t="n">
+      <c r="D182" s="3" t="n"/>
+      <c r="E182" s="3" t="n"/>
+      <c r="F182" s="3" t="n"/>
+      <c r="G182" s="3" t="n"/>
+      <c r="H182" s="3" t="n"/>
+      <c r="I182" s="3" t="n"/>
+      <c r="J182" s="5" t="n">
         <v>8440.290000000001</v>
       </c>
-      <c r="K180" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L180" s="5" t="n">
+      <c r="K182" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L182" s="5" t="n">
         <v>8440.290000000001</v>
       </c>
     </row>
-    <row r="181" ht="18" customHeight="1">
-      <c r="A181" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B181" s="6" t="inlineStr">
+    <row r="183" ht="18" customHeight="1">
+      <c r="A183" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="inlineStr">
         <is>
           <t>MMGMIR61037</t>
         </is>
       </c>
-      <c r="C181" s="7" t="inlineStr">
+      <c r="C183" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 B UHF SORGULAMALI ALICI</t>
         </is>
       </c>
-      <c r="D181" s="6" t="inlineStr">
+      <c r="D183" s="6" t="inlineStr">
         <is>
           <t>GMP-101-230099</t>
         </is>
       </c>
-      <c r="E181" s="7" t="inlineStr">
+      <c r="E183" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 B UHF SORGULAMALI ALICI</t>
         </is>
       </c>
-      <c r="F181" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G181" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H181" s="9" t="n">
+      <c r="F183" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G183" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H183" s="9" t="n">
         <v>8440.2893</v>
       </c>
-      <c r="I181" s="10" t="n">
+      <c r="I183" s="10" t="n">
         <v>8440.290000000001</v>
       </c>
-      <c r="J181" s="6" t="n"/>
-      <c r="K181" s="6" t="n"/>
-      <c r="L181" s="6" t="n"/>
-    </row>
-    <row r="182" ht="20" customHeight="1">
-      <c r="A182" s="11" t="inlineStr">
+      <c r="J183" s="6" t="n"/>
+      <c r="K183" s="6" t="n"/>
+      <c r="L183" s="6" t="n"/>
+    </row>
+    <row r="184" ht="20" customHeight="1">
+      <c r="A184" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B182" s="11" t="inlineStr">
+      <c r="B184" s="11" t="inlineStr">
         <is>
           <t>MMGMIR61037</t>
         </is>
       </c>
-      <c r="C182" s="12" t="inlineStr">
+      <c r="C184" s="12" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 B UHF SORGULAMALI ALICI</t>
         </is>
       </c>
-      <c r="D182" s="11" t="n"/>
-      <c r="E182" s="11" t="n"/>
-      <c r="F182" s="11" t="n"/>
-      <c r="G182" s="11" t="n"/>
-      <c r="H182" s="11" t="n"/>
-      <c r="I182" s="11" t="n"/>
-      <c r="J182" s="13" t="n">
+      <c r="D184" s="11" t="n"/>
+      <c r="E184" s="11" t="n"/>
+      <c r="F184" s="11" t="n"/>
+      <c r="G184" s="11" t="n"/>
+      <c r="H184" s="11" t="n"/>
+      <c r="I184" s="11" t="n"/>
+      <c r="J184" s="13" t="n">
         <v>8440.290000000001</v>
       </c>
-      <c r="K182" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L182" s="13" t="n">
+      <c r="K184" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L184" s="13" t="n">
         <v>8440.290000000001</v>
       </c>
     </row>
-    <row r="183" ht="6" customHeight="1"/>
-    <row r="184" ht="22" customHeight="1">
-      <c r="A184" s="3" t="inlineStr">
+    <row r="185" ht="6" customHeight="1"/>
+    <row r="186" ht="22" customHeight="1">
+      <c r="A186" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B184" s="3" t="inlineStr">
+      <c r="B186" s="3" t="inlineStr">
         <is>
           <t>MMGMIR61038</t>
         </is>
       </c>
-      <c r="C184" s="4" t="inlineStr">
+      <c r="C186" s="4" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 UHF AKÜLÜ GÜNEŞ PANELLİ ALICI</t>
         </is>
       </c>
-      <c r="D184" s="3" t="n"/>
-      <c r="E184" s="3" t="n"/>
-      <c r="F184" s="3" t="n"/>
-      <c r="G184" s="3" t="n"/>
-      <c r="H184" s="3" t="n"/>
-      <c r="I184" s="3" t="n"/>
-      <c r="J184" s="5" t="n">
+      <c r="D186" s="3" t="n"/>
+      <c r="E186" s="3" t="n"/>
+      <c r="F186" s="3" t="n"/>
+      <c r="G186" s="3" t="n"/>
+      <c r="H186" s="3" t="n"/>
+      <c r="I186" s="3" t="n"/>
+      <c r="J186" s="5" t="n">
         <v>4572.99</v>
       </c>
-      <c r="K184" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L184" s="5" t="n">
+      <c r="K186" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L186" s="5" t="n">
         <v>4572.99</v>
       </c>
     </row>
-    <row r="185" ht="18" customHeight="1">
-      <c r="A185" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B185" s="6" t="inlineStr">
+    <row r="187" ht="18" customHeight="1">
+      <c r="A187" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B187" s="6" t="inlineStr">
         <is>
           <t>MMGMIR61038</t>
         </is>
       </c>
-      <c r="C185" s="7" t="inlineStr">
+      <c r="C187" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 UHF AKÜLÜ GÜNEŞ PANELLİ ALICI</t>
         </is>
       </c>
-      <c r="D185" s="6" t="inlineStr">
+      <c r="D187" s="6" t="inlineStr">
         <is>
           <t>GMP-101-230100</t>
         </is>
       </c>
-      <c r="E185" s="7" t="inlineStr">
+      <c r="E187" s="7" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 UHF AKÜLÜ GÜNEŞ PANELLİ ALICI</t>
         </is>
       </c>
-      <c r="F185" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G185" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H185" s="9" t="n">
+      <c r="F187" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G187" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H187" s="9" t="n">
         <v>4572.994</v>
       </c>
-      <c r="I185" s="10" t="n">
+      <c r="I187" s="10" t="n">
         <v>4572.99</v>
       </c>
-      <c r="J185" s="6" t="n"/>
-      <c r="K185" s="6" t="n"/>
-      <c r="L185" s="6" t="n"/>
-    </row>
-    <row r="186" ht="20" customHeight="1">
-      <c r="A186" s="11" t="inlineStr">
+      <c r="J187" s="6" t="n"/>
+      <c r="K187" s="6" t="n"/>
+      <c r="L187" s="6" t="n"/>
+    </row>
+    <row r="188" ht="20" customHeight="1">
+      <c r="A188" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B186" s="11" t="inlineStr">
+      <c r="B188" s="11" t="inlineStr">
         <is>
           <t>MMGMIR61038</t>
         </is>
       </c>
-      <c r="C186" s="12" t="inlineStr">
+      <c r="C188" s="12" t="inlineStr">
         <is>
           <t>GEMVOICE IR-610 UHF AKÜLÜ GÜNEŞ PANELLİ ALICI</t>
         </is>
       </c>
-      <c r="D186" s="11" t="n"/>
-      <c r="E186" s="11" t="n"/>
-      <c r="F186" s="11" t="n"/>
-      <c r="G186" s="11" t="n"/>
-      <c r="H186" s="11" t="n"/>
-      <c r="I186" s="11" t="n"/>
-      <c r="J186" s="13" t="n">
+      <c r="D188" s="11" t="n"/>
+      <c r="E188" s="11" t="n"/>
+      <c r="F188" s="11" t="n"/>
+      <c r="G188" s="11" t="n"/>
+      <c r="H188" s="11" t="n"/>
+      <c r="I188" s="11" t="n"/>
+      <c r="J188" s="13" t="n">
         <v>4572.99</v>
       </c>
-      <c r="K186" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L186" s="13" t="n">
+      <c r="K188" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L188" s="13" t="n">
         <v>4572.99</v>
       </c>
     </row>
-    <row r="187" ht="6" customHeight="1"/>
-    <row r="188" ht="22" customHeight="1">
-      <c r="A188" s="3" t="inlineStr">
+    <row r="189" ht="6" customHeight="1"/>
+    <row r="190" ht="22" customHeight="1">
+      <c r="A190" s="3" t="inlineStr">
         <is>
           <t>MAMÜL</t>
         </is>
       </c>
-      <c r="B188" s="3" t="inlineStr">
+      <c r="B190" s="3" t="inlineStr">
         <is>
           <t>MMPBIŞIK01</t>
         </is>
       </c>
-      <c r="C188" s="4" t="inlineStr">
+      <c r="C190" s="4" t="inlineStr">
         <is>
           <t>PORTATİF IŞIK KAYNAĞI</t>
         </is>
       </c>
-      <c r="D188" s="3" t="n"/>
-      <c r="E188" s="3" t="n"/>
-      <c r="F188" s="3" t="n"/>
-      <c r="G188" s="3" t="n"/>
-      <c r="H188" s="3" t="n"/>
-      <c r="I188" s="3" t="n"/>
-      <c r="J188" s="5" t="n">
+      <c r="D190" s="3" t="n"/>
+      <c r="E190" s="3" t="n"/>
+      <c r="F190" s="3" t="n"/>
+      <c r="G190" s="3" t="n"/>
+      <c r="H190" s="3" t="n"/>
+      <c r="I190" s="3" t="n"/>
+      <c r="J190" s="5" t="n">
         <v>10096.09</v>
       </c>
-      <c r="K188" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L188" s="5" t="n">
+      <c r="K190" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L190" s="5" t="n">
         <v>10096.09</v>
       </c>
     </row>
-    <row r="189" ht="18" customHeight="1">
-      <c r="A189" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B189" s="6" t="inlineStr">
+    <row r="191" ht="18" customHeight="1">
+      <c r="A191" s="14" t="inlineStr">
+        <is>
+          <t>ALT-MAMÜL</t>
+        </is>
+      </c>
+      <c r="B191" s="14" t="inlineStr">
         <is>
           <t>MMPBIŞIK01</t>
         </is>
       </c>
-      <c r="C189" s="7" t="inlineStr">
+      <c r="C191" s="15" t="inlineStr">
         <is>
           <t>PORTATİF IŞIK KAYNAĞI</t>
         </is>
       </c>
-      <c r="D189" s="6" t="inlineStr">
+      <c r="D191" s="14" t="inlineStr">
         <is>
           <t>GMP-101-230107</t>
         </is>
       </c>
-      <c r="E189" s="7" t="inlineStr">
+      <c r="E191" s="15" t="inlineStr">
         <is>
           <t>ÇOK DALGA BOYLU PORTATİF IŞIK KAYNAĞI</t>
         </is>
       </c>
-      <c r="F189" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G189" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H189" s="9" t="n">
+      <c r="F191" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G191" s="14" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H191" s="17" t="n">
         <v>10096.0919</v>
       </c>
-      <c r="I189" s="10" t="n">
+      <c r="I191" s="18" t="n">
         <v>10096.09</v>
       </c>
-      <c r="J189" s="6" t="n"/>
-      <c r="K189" s="6" t="n"/>
-      <c r="L189" s="6" t="n"/>
-    </row>
-    <row r="190" ht="20" customHeight="1">
-      <c r="A190" s="11" t="inlineStr">
-        <is>
-          <t>TOPLAM</t>
-        </is>
-      </c>
-      <c r="B190" s="11" t="inlineStr">
+      <c r="J191" s="14" t="n"/>
+      <c r="K191" s="14" t="n"/>
+      <c r="L191" s="14" t="n"/>
+    </row>
+    <row r="192" ht="18" customHeight="1">
+      <c r="A192" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B192" s="6" t="inlineStr">
         <is>
           <t>MMPBIŞIK01</t>
         </is>
       </c>
-      <c r="C190" s="12" t="inlineStr">
+      <c r="C192" s="7" t="inlineStr">
         <is>
           <t>PORTATİF IŞIK KAYNAĞI</t>
         </is>
       </c>
-      <c r="D190" s="11" t="n"/>
-      <c r="E190" s="11" t="n"/>
-      <c r="F190" s="11" t="n"/>
-      <c r="G190" s="11" t="n"/>
-      <c r="H190" s="11" t="n"/>
-      <c r="I190" s="11" t="n"/>
-      <c r="J190" s="13" t="n">
-        <v>10096.09</v>
-      </c>
-      <c r="K190" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L190" s="13" t="n">
-        <v>10096.09</v>
-      </c>
-    </row>
-    <row r="191" ht="6" customHeight="1"/>
-    <row r="192" ht="22" customHeight="1">
-      <c r="A192" s="3" t="inlineStr">
-        <is>
-          <t>MAMÜL</t>
-        </is>
-      </c>
-      <c r="B192" s="3" t="inlineStr">
-        <is>
-          <t>MMSBIŞIK002</t>
-        </is>
-      </c>
-      <c r="C192" s="4" t="inlineStr">
-        <is>
-          <t>ÇOK DALGA BOYLU IŞIK KAYNAĞI-2</t>
-        </is>
-      </c>
-      <c r="D192" s="3" t="n"/>
-      <c r="E192" s="3" t="n"/>
-      <c r="F192" s="3" t="n"/>
-      <c r="G192" s="3" t="n"/>
-      <c r="H192" s="3" t="n"/>
-      <c r="I192" s="3" t="n"/>
-      <c r="J192" s="5" t="n">
-        <v>73364.19</v>
-      </c>
-      <c r="K192" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L192" s="5" t="n">
-        <v>73364.19</v>
-      </c>
+      <c r="D192" s="6" t="inlineStr">
+        <is>
+          <t>GMP-300-230001</t>
+        </is>
+      </c>
+      <c r="E192" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PORTATİF DİZGİ DRİVER KART  (SERİ ÜRTETİM) 
+</t>
+        </is>
+      </c>
+      <c r="F192" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G192" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H192" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I192" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" s="6" t="n"/>
+      <c r="K192" s="6" t="n"/>
+      <c r="L192" s="6" t="n"/>
     </row>
     <row r="193" ht="18" customHeight="1">
       <c r="A193" s="6" t="inlineStr">
@@ -6224,22 +6320,23 @@
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>MMSBIŞIK002</t>
+          <t>MMPBIŞIK01</t>
         </is>
       </c>
       <c r="C193" s="7" t="inlineStr">
         <is>
-          <t>ÇOK DALGA BOYLU IŞIK KAYNAĞI-2</t>
+          <t>PORTATİF IŞIK KAYNAĞI</t>
         </is>
       </c>
       <c r="D193" s="6" t="inlineStr">
         <is>
-          <t>GMP-101-230108</t>
+          <t>GMP-300-230002</t>
         </is>
       </c>
       <c r="E193" s="7" t="inlineStr">
         <is>
-          <t>ÇOK DALGA BOYLU SABİT IŞIK KAYNAĞI (PS10-F)</t>
+          <t xml:space="preserve">    PORTATİF HALL SENSOR KART  (SERİ ÜRETİM) 
+</t>
         </is>
       </c>
       <c r="F193" s="8" t="n">
@@ -6251,79 +6348,149 @@
         </is>
       </c>
       <c r="H193" s="9" t="n">
-        <v>73364.19</v>
+        <v>0</v>
       </c>
       <c r="I193" s="10" t="n">
-        <v>73364.19</v>
+        <v>0</v>
       </c>
       <c r="J193" s="6" t="n"/>
       <c r="K193" s="6" t="n"/>
       <c r="L193" s="6" t="n"/>
     </row>
-    <row r="194" ht="20" customHeight="1">
-      <c r="A194" s="11" t="inlineStr">
-        <is>
-          <t>TOPLAM</t>
-        </is>
-      </c>
-      <c r="B194" s="11" t="inlineStr">
-        <is>
-          <t>MMSBIŞIK002</t>
-        </is>
-      </c>
-      <c r="C194" s="12" t="inlineStr">
-        <is>
-          <t>ÇOK DALGA BOYLU IŞIK KAYNAĞI-2</t>
-        </is>
-      </c>
-      <c r="D194" s="11" t="n"/>
-      <c r="E194" s="11" t="n"/>
-      <c r="F194" s="11" t="n"/>
-      <c r="G194" s="11" t="n"/>
-      <c r="H194" s="11" t="n"/>
-      <c r="I194" s="11" t="n"/>
-      <c r="J194" s="13" t="n">
-        <v>73364.19</v>
-      </c>
-      <c r="K194" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L194" s="13" t="n">
-        <v>73364.19</v>
-      </c>
-    </row>
-    <row r="195" ht="6" customHeight="1"/>
-    <row r="196" ht="22" customHeight="1">
-      <c r="A196" s="3" t="inlineStr">
-        <is>
-          <t>MAMÜL</t>
-        </is>
-      </c>
-      <c r="B196" s="3" t="inlineStr">
-        <is>
-          <t>MMUHF000001</t>
-        </is>
-      </c>
-      <c r="C196" s="4" t="inlineStr">
-        <is>
-          <t>TX IR-610 UHF VK VERİCİ</t>
-        </is>
-      </c>
-      <c r="D196" s="3" t="n"/>
-      <c r="E196" s="3" t="n"/>
-      <c r="F196" s="3" t="n"/>
-      <c r="G196" s="3" t="n"/>
-      <c r="H196" s="3" t="n"/>
-      <c r="I196" s="3" t="n"/>
-      <c r="J196" s="5" t="n">
-        <v>18935.77</v>
-      </c>
-      <c r="K196" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L196" s="5" t="n">
-        <v>18935.77</v>
-      </c>
+    <row r="194" ht="18" customHeight="1">
+      <c r="A194" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B194" s="6" t="inlineStr">
+        <is>
+          <t>MMPBIŞIK01</t>
+        </is>
+      </c>
+      <c r="C194" s="7" t="inlineStr">
+        <is>
+          <t>PORTATİF IŞIK KAYNAĞI</t>
+        </is>
+      </c>
+      <c r="D194" s="6" t="inlineStr">
+        <is>
+          <t>GMP-300-230003</t>
+        </is>
+      </c>
+      <c r="E194" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PORTATİF DİZGİ BUTON KART (Seri Üretim) 
+</t>
+        </is>
+      </c>
+      <c r="F194" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H194" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I194" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" s="6" t="n"/>
+      <c r="K194" s="6" t="n"/>
+      <c r="L194" s="6" t="n"/>
+    </row>
+    <row r="195" ht="18" customHeight="1">
+      <c r="A195" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B195" s="6" t="inlineStr">
+        <is>
+          <t>MMPBIŞIK01</t>
+        </is>
+      </c>
+      <c r="C195" s="7" t="inlineStr">
+        <is>
+          <t>PORTATİF IŞIK KAYNAĞI</t>
+        </is>
+      </c>
+      <c r="D195" s="6" t="inlineStr">
+        <is>
+          <t>GMP-300-230004</t>
+        </is>
+      </c>
+      <c r="E195" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PORTATİF DİZGİ POKO PİN KART (Seri Üretim) 
+</t>
+        </is>
+      </c>
+      <c r="F195" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H195" s="9" t="n">
+        <v>199.74</v>
+      </c>
+      <c r="I195" s="10" t="n">
+        <v>199.74</v>
+      </c>
+      <c r="J195" s="6" t="n"/>
+      <c r="K195" s="6" t="n"/>
+      <c r="L195" s="6" t="n"/>
+    </row>
+    <row r="196" ht="18" customHeight="1">
+      <c r="A196" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B196" s="6" t="inlineStr">
+        <is>
+          <t>MMPBIŞIK01</t>
+        </is>
+      </c>
+      <c r="C196" s="7" t="inlineStr">
+        <is>
+          <t>PORTATİF IŞIK KAYNAĞI</t>
+        </is>
+      </c>
+      <c r="D196" s="6" t="inlineStr">
+        <is>
+          <t>GMP-300-230005</t>
+        </is>
+      </c>
+      <c r="E196" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PORTATİF DİZGİ LED KART (SERİ ÜRETİM)
+</t>
+        </is>
+      </c>
+      <c r="F196" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H196" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I196" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" s="6" t="n"/>
+      <c r="K196" s="6" t="n"/>
+      <c r="L196" s="6" t="n"/>
     </row>
     <row r="197" ht="18" customHeight="1">
       <c r="A197" s="6" t="inlineStr">
@@ -6333,22 +6500,22 @@
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>MMUHF000001</t>
+          <t>MMPBIŞIK01</t>
         </is>
       </c>
       <c r="C197" s="7" t="inlineStr">
         <is>
-          <t>TX IR-610 UHF VK VERİCİ</t>
+          <t>PORTATİF IŞIK KAYNAĞI</t>
         </is>
       </c>
       <c r="D197" s="6" t="inlineStr">
         <is>
-          <t>GMP-101-230109</t>
+          <t>JANDPORTAKS002</t>
         </is>
       </c>
       <c r="E197" s="7" t="inlineStr">
         <is>
-          <t>TX IR-610 UHF VK VERİCİ</t>
+          <t xml:space="preserve">    JANDARMA PORTATİF AKSESUAR GRUBU</t>
         </is>
       </c>
       <c r="F197" s="8" t="n">
@@ -6360,79 +6527,147 @@
         </is>
       </c>
       <c r="H197" s="9" t="n">
-        <v>18935.7702</v>
+        <v>0</v>
       </c>
       <c r="I197" s="10" t="n">
-        <v>18935.77</v>
+        <v>0</v>
       </c>
       <c r="J197" s="6" t="n"/>
       <c r="K197" s="6" t="n"/>
       <c r="L197" s="6" t="n"/>
     </row>
-    <row r="198" ht="20" customHeight="1">
-      <c r="A198" s="11" t="inlineStr">
-        <is>
-          <t>TOPLAM</t>
-        </is>
-      </c>
-      <c r="B198" s="11" t="inlineStr">
-        <is>
-          <t>MMUHF000001</t>
-        </is>
-      </c>
-      <c r="C198" s="12" t="inlineStr">
-        <is>
-          <t>TX IR-610 UHF VK VERİCİ</t>
-        </is>
-      </c>
-      <c r="D198" s="11" t="n"/>
-      <c r="E198" s="11" t="n"/>
-      <c r="F198" s="11" t="n"/>
-      <c r="G198" s="11" t="n"/>
-      <c r="H198" s="11" t="n"/>
-      <c r="I198" s="11" t="n"/>
-      <c r="J198" s="13" t="n">
-        <v>18935.77</v>
-      </c>
-      <c r="K198" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L198" s="13" t="n">
-        <v>18935.77</v>
-      </c>
-    </row>
-    <row r="199" ht="6" customHeight="1"/>
-    <row r="200" ht="22" customHeight="1">
-      <c r="A200" s="3" t="inlineStr">
-        <is>
-          <t>MAMÜL</t>
-        </is>
-      </c>
-      <c r="B200" s="3" t="inlineStr">
-        <is>
-          <t>MMUHF000003</t>
-        </is>
-      </c>
-      <c r="C200" s="4" t="inlineStr">
-        <is>
-          <t>TX IR-610 UHF CC VERİCİ</t>
-        </is>
-      </c>
-      <c r="D200" s="3" t="n"/>
-      <c r="E200" s="3" t="n"/>
-      <c r="F200" s="3" t="n"/>
-      <c r="G200" s="3" t="n"/>
-      <c r="H200" s="3" t="n"/>
-      <c r="I200" s="3" t="n"/>
-      <c r="J200" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K200" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L200" s="5" t="n">
-        <v>0</v>
-      </c>
+    <row r="198" ht="18" customHeight="1">
+      <c r="A198" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B198" s="6" t="inlineStr">
+        <is>
+          <t>MMPBIŞIK01</t>
+        </is>
+      </c>
+      <c r="C198" s="7" t="inlineStr">
+        <is>
+          <t>PORTATİF IŞIK KAYNAĞI</t>
+        </is>
+      </c>
+      <c r="D198" s="6" t="inlineStr">
+        <is>
+          <t>YMB-V00R00-220005</t>
+        </is>
+      </c>
+      <c r="E198" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    OKÜLER BÜTÜNÜ</t>
+        </is>
+      </c>
+      <c r="F198" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G198" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H198" s="9" t="n">
+        <v>3199.8471</v>
+      </c>
+      <c r="I198" s="10" t="n">
+        <v>3199.85</v>
+      </c>
+      <c r="J198" s="6" t="n"/>
+      <c r="K198" s="6" t="n"/>
+      <c r="L198" s="6" t="n"/>
+    </row>
+    <row r="199" ht="18" customHeight="1">
+      <c r="A199" s="14" t="inlineStr">
+        <is>
+          <t>ALT-MAMÜL</t>
+        </is>
+      </c>
+      <c r="B199" s="14" t="inlineStr">
+        <is>
+          <t>MMPBIŞIK01</t>
+        </is>
+      </c>
+      <c r="C199" s="15" t="inlineStr">
+        <is>
+          <t>PORTATİF IŞIK KAYNAĞI</t>
+        </is>
+      </c>
+      <c r="D199" s="14" t="inlineStr">
+        <is>
+          <t>YMB-V00R00-220007</t>
+        </is>
+      </c>
+      <c r="E199" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    LED BÜTÜNÜ</t>
+        </is>
+      </c>
+      <c r="F199" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G199" s="14" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H199" s="17" t="n">
+        <v>199.74</v>
+      </c>
+      <c r="I199" s="18" t="n">
+        <v>199.74</v>
+      </c>
+      <c r="J199" s="14" t="n"/>
+      <c r="K199" s="14" t="n"/>
+      <c r="L199" s="14" t="n"/>
+    </row>
+    <row r="200" ht="18" customHeight="1">
+      <c r="A200" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B200" s="6" t="inlineStr">
+        <is>
+          <t>MMPBIŞIK01</t>
+        </is>
+      </c>
+      <c r="C200" s="7" t="inlineStr">
+        <is>
+          <t>PORTATİF IŞIK KAYNAĞI</t>
+        </is>
+      </c>
+      <c r="D200" s="6" t="inlineStr">
+        <is>
+          <t>GMP-300-230004</t>
+        </is>
+      </c>
+      <c r="E200" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        PORTATİF DİZGİ POKO PİN KART (Seri Üretim) 
+</t>
+        </is>
+      </c>
+      <c r="F200" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H200" s="9" t="n">
+        <v>199.74</v>
+      </c>
+      <c r="I200" s="10" t="n">
+        <v>199.74</v>
+      </c>
+      <c r="J200" s="6" t="n"/>
+      <c r="K200" s="6" t="n"/>
+      <c r="L200" s="6" t="n"/>
     </row>
     <row r="201" ht="18" customHeight="1">
       <c r="A201" s="6" t="inlineStr">
@@ -6442,22 +6677,23 @@
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>MMUHF000003</t>
+          <t>MMPBIŞIK01</t>
         </is>
       </c>
       <c r="C201" s="7" t="inlineStr">
         <is>
-          <t>TX IR-610 UHF CC VERİCİ</t>
+          <t>PORTATİF IŞIK KAYNAĞI</t>
         </is>
       </c>
       <c r="D201" s="6" t="inlineStr">
         <is>
-          <t>GMP-101-230111</t>
+          <t>GMP-300-230005</t>
         </is>
       </c>
       <c r="E201" s="7" t="inlineStr">
         <is>
-          <t>TX IR-610 UHF CC VERİCİ</t>
+          <t xml:space="preserve">        PORTATİF DİZGİ LED KART (SERİ ÜRETİM)
+</t>
         </is>
       </c>
       <c r="F201" s="8" t="n">
@@ -6478,70 +6714,137 @@
       <c r="K201" s="6" t="n"/>
       <c r="L201" s="6" t="n"/>
     </row>
-    <row r="202" ht="20" customHeight="1">
-      <c r="A202" s="11" t="inlineStr">
-        <is>
-          <t>TOPLAM</t>
-        </is>
-      </c>
-      <c r="B202" s="11" t="inlineStr">
-        <is>
-          <t>MMUHF000003</t>
-        </is>
-      </c>
-      <c r="C202" s="12" t="inlineStr">
-        <is>
-          <t>TX IR-610 UHF CC VERİCİ</t>
-        </is>
-      </c>
-      <c r="D202" s="11" t="n"/>
-      <c r="E202" s="11" t="n"/>
-      <c r="F202" s="11" t="n"/>
-      <c r="G202" s="11" t="n"/>
-      <c r="H202" s="11" t="n"/>
-      <c r="I202" s="11" t="n"/>
-      <c r="J202" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K202" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L202" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203" ht="6" customHeight="1"/>
-    <row r="204" ht="22" customHeight="1">
-      <c r="A204" s="3" t="inlineStr">
-        <is>
-          <t>MAMÜL</t>
-        </is>
-      </c>
-      <c r="B204" s="3" t="inlineStr">
-        <is>
-          <t>MMUHF000005</t>
-        </is>
-      </c>
-      <c r="C204" s="4" t="inlineStr">
-        <is>
-          <t>TX IR-610 UHF CC EKRANLI VERİCİ</t>
-        </is>
-      </c>
-      <c r="D204" s="3" t="n"/>
-      <c r="E204" s="3" t="n"/>
-      <c r="F204" s="3" t="n"/>
-      <c r="G204" s="3" t="n"/>
-      <c r="H204" s="3" t="n"/>
-      <c r="I204" s="3" t="n"/>
-      <c r="J204" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K204" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L204" s="5" t="n">
-        <v>0</v>
-      </c>
+    <row r="202" ht="18" customHeight="1">
+      <c r="A202" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B202" s="6" t="inlineStr">
+        <is>
+          <t>MMPBIŞIK01</t>
+        </is>
+      </c>
+      <c r="C202" s="7" t="inlineStr">
+        <is>
+          <t>PORTATİF IŞIK KAYNAĞI</t>
+        </is>
+      </c>
+      <c r="D202" s="6" t="inlineStr">
+        <is>
+          <t>YMB-V00R00-220008</t>
+        </is>
+      </c>
+      <c r="E202" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SOĞUTUCU GÖVDE BÜTÜNÜ</t>
+        </is>
+      </c>
+      <c r="F202" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G202" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H202" s="9" t="n">
+        <v>1498.3051</v>
+      </c>
+      <c r="I202" s="10" t="n">
+        <v>1498.31</v>
+      </c>
+      <c r="J202" s="6" t="n"/>
+      <c r="K202" s="6" t="n"/>
+      <c r="L202" s="6" t="n"/>
+    </row>
+    <row r="203" ht="18" customHeight="1">
+      <c r="A203" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B203" s="6" t="inlineStr">
+        <is>
+          <t>MMPBIŞIK01</t>
+        </is>
+      </c>
+      <c r="C203" s="7" t="inlineStr">
+        <is>
+          <t>PORTATİF IŞIK KAYNAĞI</t>
+        </is>
+      </c>
+      <c r="D203" s="6" t="inlineStr">
+        <is>
+          <t>YMB-V00R00-220009</t>
+        </is>
+      </c>
+      <c r="E203" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    BUTON BÜTÜNÜ</t>
+        </is>
+      </c>
+      <c r="F203" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G203" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H203" s="9" t="n">
+        <v>602.6314</v>
+      </c>
+      <c r="I203" s="10" t="n">
+        <v>602.63</v>
+      </c>
+      <c r="J203" s="6" t="n"/>
+      <c r="K203" s="6" t="n"/>
+      <c r="L203" s="6" t="n"/>
+    </row>
+    <row r="204" ht="18" customHeight="1">
+      <c r="A204" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B204" s="6" t="inlineStr">
+        <is>
+          <t>MMPBIŞIK01</t>
+        </is>
+      </c>
+      <c r="C204" s="7" t="inlineStr">
+        <is>
+          <t>PORTATİF IŞIK KAYNAĞI</t>
+        </is>
+      </c>
+      <c r="D204" s="6" t="inlineStr">
+        <is>
+          <t>YMB-V00R00-220010</t>
+        </is>
+      </c>
+      <c r="E204" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    EKRAN BÜTÜNÜ</t>
+        </is>
+      </c>
+      <c r="F204" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G204" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H204" s="9" t="n">
+        <v>198.7322</v>
+      </c>
+      <c r="I204" s="10" t="n">
+        <v>198.73</v>
+      </c>
+      <c r="J204" s="6" t="n"/>
+      <c r="K204" s="6" t="n"/>
+      <c r="L204" s="6" t="n"/>
     </row>
     <row r="205" ht="18" customHeight="1">
       <c r="A205" s="6" t="inlineStr">
@@ -6551,22 +6854,22 @@
       </c>
       <c r="B205" s="6" t="inlineStr">
         <is>
-          <t>MMUHF000005</t>
+          <t>MMPBIŞIK01</t>
         </is>
       </c>
       <c r="C205" s="7" t="inlineStr">
         <is>
-          <t>TX IR-610 UHF CC EKRANLI VERİCİ</t>
+          <t>PORTATİF IŞIK KAYNAĞI</t>
         </is>
       </c>
       <c r="D205" s="6" t="inlineStr">
         <is>
-          <t>GMP-101-230112</t>
+          <t>YMB-V00R00-220011</t>
         </is>
       </c>
       <c r="E205" s="7" t="inlineStr">
         <is>
-          <t>TX IR-610 UHF CC EKRANLI VERİCİ</t>
+          <t xml:space="preserve">    ANA GÖVDE BÜTÜNÜ</t>
         </is>
       </c>
       <c r="F205" s="8" t="n">
@@ -6578,10 +6881,10 @@
         </is>
       </c>
       <c r="H205" s="9" t="n">
-        <v>0</v>
+        <v>4197.0961</v>
       </c>
       <c r="I205" s="10" t="n">
-        <v>0</v>
+        <v>4197.1</v>
       </c>
       <c r="J205" s="6" t="n"/>
       <c r="K205" s="6" t="n"/>
@@ -6595,12 +6898,12 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>MMUHF000005</t>
+          <t>MMPBIŞIK01</t>
         </is>
       </c>
       <c r="C206" s="12" t="inlineStr">
         <is>
-          <t>TX IR-610 UHF CC EKRANLI VERİCİ</t>
+          <t>PORTATİF IŞIK KAYNAĞI</t>
         </is>
       </c>
       <c r="D206" s="11" t="n"/>
@@ -6610,13 +6913,13 @@
       <c r="H206" s="11" t="n"/>
       <c r="I206" s="11" t="n"/>
       <c r="J206" s="13" t="n">
-        <v>0</v>
+        <v>10096.09</v>
       </c>
       <c r="K206" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L206" s="13" t="n">
-        <v>0</v>
+        <v>10096.09</v>
       </c>
     </row>
     <row r="207" ht="6" customHeight="1"/>
@@ -6628,12 +6931,12 @@
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>MMUHF000007</t>
+          <t>MMSBIŞIK002</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>TX IR-610 UHF CC SORGULAMALI VERİCİ</t>
+          <t>ÇOK DALGA BOYLU IŞIK KAYNAĞI-2</t>
         </is>
       </c>
       <c r="D208" s="3" t="n"/>
@@ -6643,13 +6946,13 @@
       <c r="H208" s="3" t="n"/>
       <c r="I208" s="3" t="n"/>
       <c r="J208" s="5" t="n">
-        <v>0</v>
+        <v>73364.19</v>
       </c>
       <c r="K208" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L208" s="5" t="n">
-        <v>0</v>
+        <v>73364.19</v>
       </c>
     </row>
     <row r="209" ht="18" customHeight="1">
@@ -6660,22 +6963,22 @@
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t>MMUHF000007</t>
+          <t>MMSBIŞIK002</t>
         </is>
       </c>
       <c r="C209" s="7" t="inlineStr">
         <is>
-          <t>TX IR-610 UHF CC SORGULAMALI VERİCİ</t>
+          <t>ÇOK DALGA BOYLU IŞIK KAYNAĞI-2</t>
         </is>
       </c>
       <c r="D209" s="6" t="inlineStr">
         <is>
-          <t>GMP-101-230113</t>
+          <t>GMP-101-230108</t>
         </is>
       </c>
       <c r="E209" s="7" t="inlineStr">
         <is>
-          <t>TX IR-610 UHF CC SORGULAMALI VERİCİ</t>
+          <t>ÇOK DALGA BOYLU SABİT IŞIK KAYNAĞI (PS10-F)</t>
         </is>
       </c>
       <c r="F209" s="8" t="n">
@@ -6687,10 +6990,10 @@
         </is>
       </c>
       <c r="H209" s="9" t="n">
-        <v>0</v>
+        <v>73364.19</v>
       </c>
       <c r="I209" s="10" t="n">
-        <v>0</v>
+        <v>73364.19</v>
       </c>
       <c r="J209" s="6" t="n"/>
       <c r="K209" s="6" t="n"/>
@@ -6704,12 +7007,12 @@
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t>MMUHF000007</t>
+          <t>MMSBIŞIK002</t>
         </is>
       </c>
       <c r="C210" s="12" t="inlineStr">
         <is>
-          <t>TX IR-610 UHF CC SORGULAMALI VERİCİ</t>
+          <t>ÇOK DALGA BOYLU IŞIK KAYNAĞI-2</t>
         </is>
       </c>
       <c r="D210" s="11" t="n"/>
@@ -6719,13 +7022,13 @@
       <c r="H210" s="11" t="n"/>
       <c r="I210" s="11" t="n"/>
       <c r="J210" s="13" t="n">
-        <v>0</v>
+        <v>73364.19</v>
       </c>
       <c r="K210" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L210" s="13" t="n">
-        <v>0</v>
+        <v>73364.19</v>
       </c>
     </row>
     <row r="211" ht="6" customHeight="1"/>
@@ -6737,12 +7040,12 @@
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>MMUHF000008</t>
+          <t>MMUHF000001</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>TX IR-610 UHF CEPTE ANONSLU VERİCİ</t>
+          <t>TX IR-610 UHF VK VERİCİ</t>
         </is>
       </c>
       <c r="D212" s="3" t="n"/>
@@ -6752,13 +7055,13 @@
       <c r="H212" s="3" t="n"/>
       <c r="I212" s="3" t="n"/>
       <c r="J212" s="5" t="n">
-        <v>2932.86</v>
+        <v>18935.77</v>
       </c>
       <c r="K212" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L212" s="5" t="n">
-        <v>2932.86</v>
+        <v>18935.77</v>
       </c>
     </row>
     <row r="213" ht="18" customHeight="1">
@@ -6769,22 +7072,22 @@
       </c>
       <c r="B213" s="6" t="inlineStr">
         <is>
-          <t>MMUHF000008</t>
+          <t>MMUHF000001</t>
         </is>
       </c>
       <c r="C213" s="7" t="inlineStr">
         <is>
-          <t>TX IR-610 UHF CEPTE ANONSLU VERİCİ</t>
+          <t>TX IR-610 UHF VK VERİCİ</t>
         </is>
       </c>
       <c r="D213" s="6" t="inlineStr">
         <is>
-          <t>GMP-101-230114</t>
+          <t>GMP-101-230109</t>
         </is>
       </c>
       <c r="E213" s="7" t="inlineStr">
         <is>
-          <t>TX IR-610 UHF CEPTE ANONSLU VERİCİ</t>
+          <t>TX IR-610 UHF VK VERİCİ</t>
         </is>
       </c>
       <c r="F213" s="8" t="n">
@@ -6796,10 +7099,10 @@
         </is>
       </c>
       <c r="H213" s="9" t="n">
-        <v>2932.8601</v>
+        <v>18935.7702</v>
       </c>
       <c r="I213" s="10" t="n">
-        <v>2932.86</v>
+        <v>18935.77</v>
       </c>
       <c r="J213" s="6" t="n"/>
       <c r="K213" s="6" t="n"/>
@@ -6813,12 +7116,12 @@
       </c>
       <c r="B214" s="11" t="inlineStr">
         <is>
-          <t>MMUHF000008</t>
+          <t>MMUHF000001</t>
         </is>
       </c>
       <c r="C214" s="12" t="inlineStr">
         <is>
-          <t>TX IR-610 UHF CEPTE ANONSLU VERİCİ</t>
+          <t>TX IR-610 UHF VK VERİCİ</t>
         </is>
       </c>
       <c r="D214" s="11" t="n"/>
@@ -6828,13 +7131,13 @@
       <c r="H214" s="11" t="n"/>
       <c r="I214" s="11" t="n"/>
       <c r="J214" s="13" t="n">
-        <v>2932.86</v>
+        <v>18935.77</v>
       </c>
       <c r="K214" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L214" s="13" t="n">
-        <v>2932.86</v>
+        <v>18935.77</v>
       </c>
     </row>
     <row r="215" ht="6" customHeight="1"/>
@@ -6846,12 +7149,12 @@
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>MMVHF000001</t>
+          <t>MMUHF000003</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>TX IR-610 VHF VK VERİCİ</t>
+          <t>TX IR-610 UHF CC VERİCİ</t>
         </is>
       </c>
       <c r="D216" s="3" t="n"/>
@@ -6861,13 +7164,13 @@
       <c r="H216" s="3" t="n"/>
       <c r="I216" s="3" t="n"/>
       <c r="J216" s="5" t="n">
-        <v>11740.87</v>
+        <v>0</v>
       </c>
       <c r="K216" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L216" s="5" t="n">
-        <v>11740.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217" ht="18" customHeight="1">
@@ -6878,22 +7181,22 @@
       </c>
       <c r="B217" s="6" t="inlineStr">
         <is>
-          <t>MMVHF000001</t>
+          <t>MMUHF000003</t>
         </is>
       </c>
       <c r="C217" s="7" t="inlineStr">
         <is>
-          <t>TX IR-610 VHF VK VERİCİ</t>
+          <t>TX IR-610 UHF CC VERİCİ</t>
         </is>
       </c>
       <c r="D217" s="6" t="inlineStr">
         <is>
-          <t>GMP-101-230115</t>
+          <t>GMP-101-230111</t>
         </is>
       </c>
       <c r="E217" s="7" t="inlineStr">
         <is>
-          <t>TX IR-610 VHF VK VERİCİ</t>
+          <t>TX IR-610 UHF CC VERİCİ</t>
         </is>
       </c>
       <c r="F217" s="8" t="n">
@@ -6905,10 +7208,10 @@
         </is>
       </c>
       <c r="H217" s="9" t="n">
-        <v>11740.8713</v>
+        <v>0</v>
       </c>
       <c r="I217" s="10" t="n">
-        <v>11740.87</v>
+        <v>0</v>
       </c>
       <c r="J217" s="6" t="n"/>
       <c r="K217" s="6" t="n"/>
@@ -6922,12 +7225,12 @@
       </c>
       <c r="B218" s="11" t="inlineStr">
         <is>
-          <t>MMVHF000001</t>
+          <t>MMUHF000003</t>
         </is>
       </c>
       <c r="C218" s="12" t="inlineStr">
         <is>
-          <t>TX IR-610 VHF VK VERİCİ</t>
+          <t>TX IR-610 UHF CC VERİCİ</t>
         </is>
       </c>
       <c r="D218" s="11" t="n"/>
@@ -6937,13 +7240,13 @@
       <c r="H218" s="11" t="n"/>
       <c r="I218" s="11" t="n"/>
       <c r="J218" s="13" t="n">
-        <v>11740.87</v>
+        <v>0</v>
       </c>
       <c r="K218" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L218" s="13" t="n">
-        <v>11740.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219" ht="6" customHeight="1"/>
@@ -6955,12 +7258,12 @@
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>MMVHF000005</t>
+          <t>MMUHF000005</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>TX IR-610 VHF CC EKRANLI VERİCİ</t>
+          <t>TX IR-610 UHF CC EKRANLI VERİCİ</t>
         </is>
       </c>
       <c r="D220" s="3" t="n"/>
@@ -6987,22 +7290,22 @@
       </c>
       <c r="B221" s="6" t="inlineStr">
         <is>
-          <t>MMVHF000005</t>
+          <t>MMUHF000005</t>
         </is>
       </c>
       <c r="C221" s="7" t="inlineStr">
         <is>
-          <t>TX IR-610 VHF CC EKRANLI VERİCİ</t>
+          <t>TX IR-610 UHF CC EKRANLI VERİCİ</t>
         </is>
       </c>
       <c r="D221" s="6" t="inlineStr">
         <is>
-          <t>GMP-101-230119</t>
+          <t>GMP-101-230112</t>
         </is>
       </c>
       <c r="E221" s="7" t="inlineStr">
         <is>
-          <t>TX IR-610 VHF CC EKRANLI VERİCİ</t>
+          <t>TX IR-610 UHF CC EKRANLI VERİCİ</t>
         </is>
       </c>
       <c r="F221" s="8" t="n">
@@ -7031,12 +7334,12 @@
       </c>
       <c r="B222" s="11" t="inlineStr">
         <is>
-          <t>MMVHF000005</t>
+          <t>MMUHF000005</t>
         </is>
       </c>
       <c r="C222" s="12" t="inlineStr">
         <is>
-          <t>TX IR-610 VHF CC EKRANLI VERİCİ</t>
+          <t>TX IR-610 UHF CC EKRANLI VERİCİ</t>
         </is>
       </c>
       <c r="D222" s="11" t="n"/>
@@ -7064,12 +7367,12 @@
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>MMVHF000007</t>
+          <t>MMUHF000007</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>TX IR-610 AVK VERİCİ TELSİZSİZ</t>
+          <t>TX IR-610 UHF CC SORGULAMALI VERİCİ</t>
         </is>
       </c>
       <c r="D224" s="3" t="n"/>
@@ -7096,22 +7399,22 @@
       </c>
       <c r="B225" s="6" t="inlineStr">
         <is>
-          <t>MMVHF000007</t>
+          <t>MMUHF000007</t>
         </is>
       </c>
       <c r="C225" s="7" t="inlineStr">
         <is>
-          <t>TX IR-610 AVK VERİCİ TELSİZSİZ</t>
+          <t>TX IR-610 UHF CC SORGULAMALI VERİCİ</t>
         </is>
       </c>
       <c r="D225" s="6" t="inlineStr">
         <is>
-          <t>GMP-101-230120</t>
+          <t>GMP-101-230113</t>
         </is>
       </c>
       <c r="E225" s="7" t="inlineStr">
         <is>
-          <t>TX IR-610 AVK VERİCİ TELSİZSİZ</t>
+          <t>TX IR-610 UHF CC SORGULAMALI VERİCİ</t>
         </is>
       </c>
       <c r="F225" s="8" t="n">
@@ -7140,12 +7443,12 @@
       </c>
       <c r="B226" s="11" t="inlineStr">
         <is>
-          <t>MMVHF000007</t>
+          <t>MMUHF000007</t>
         </is>
       </c>
       <c r="C226" s="12" t="inlineStr">
         <is>
-          <t>TX IR-610 AVK VERİCİ TELSİZSİZ</t>
+          <t>TX IR-610 UHF CC SORGULAMALI VERİCİ</t>
         </is>
       </c>
       <c r="D226" s="11" t="n"/>
@@ -7173,12 +7476,12 @@
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>MMVHF000008</t>
+          <t>MMUHF000008</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>TX IR-610 VHF CC TON ATLAMALI VERİCİ</t>
+          <t>TX IR-610 UHF CEPTE ANONSLU VERİCİ</t>
         </is>
       </c>
       <c r="D228" s="3" t="n"/>
@@ -7188,13 +7491,13 @@
       <c r="H228" s="3" t="n"/>
       <c r="I228" s="3" t="n"/>
       <c r="J228" s="5" t="n">
-        <v>0</v>
+        <v>2932.86</v>
       </c>
       <c r="K228" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L228" s="5" t="n">
-        <v>0</v>
+        <v>2932.86</v>
       </c>
     </row>
     <row r="229" ht="18" customHeight="1">
@@ -7205,22 +7508,22 @@
       </c>
       <c r="B229" s="6" t="inlineStr">
         <is>
-          <t>MMVHF000008</t>
+          <t>MMUHF000008</t>
         </is>
       </c>
       <c r="C229" s="7" t="inlineStr">
         <is>
-          <t>TX IR-610 VHF CC TON ATLAMALI VERİCİ</t>
+          <t>TX IR-610 UHF CEPTE ANONSLU VERİCİ</t>
         </is>
       </c>
       <c r="D229" s="6" t="inlineStr">
         <is>
-          <t>GMP-101-230121</t>
+          <t>GMP-101-230114</t>
         </is>
       </c>
       <c r="E229" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">TX IR-610 VHF CC TON ATLAMALI VERİCİ </t>
+          <t>TX IR-610 UHF CEPTE ANONSLU VERİCİ</t>
         </is>
       </c>
       <c r="F229" s="8" t="n">
@@ -7232,10 +7535,10 @@
         </is>
       </c>
       <c r="H229" s="9" t="n">
-        <v>0</v>
+        <v>2932.8601</v>
       </c>
       <c r="I229" s="10" t="n">
-        <v>0</v>
+        <v>2932.86</v>
       </c>
       <c r="J229" s="6" t="n"/>
       <c r="K229" s="6" t="n"/>
@@ -7249,12 +7552,12 @@
       </c>
       <c r="B230" s="11" t="inlineStr">
         <is>
-          <t>MMVHF000008</t>
+          <t>MMUHF000008</t>
         </is>
       </c>
       <c r="C230" s="12" t="inlineStr">
         <is>
-          <t>TX IR-610 VHF CC TON ATLAMALI VERİCİ</t>
+          <t>TX IR-610 UHF CEPTE ANONSLU VERİCİ</t>
         </is>
       </c>
       <c r="D230" s="11" t="n"/>
@@ -7264,13 +7567,13 @@
       <c r="H230" s="11" t="n"/>
       <c r="I230" s="11" t="n"/>
       <c r="J230" s="13" t="n">
-        <v>0</v>
+        <v>2932.86</v>
       </c>
       <c r="K230" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L230" s="13" t="n">
-        <v>0</v>
+        <v>2932.86</v>
       </c>
     </row>
     <row r="231" ht="6" customHeight="1"/>
@@ -7282,12 +7585,12 @@
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>MMVHF000011</t>
+          <t>MMVHF000001</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>TX IR-610 VHF CEPTE ANONSLU VERİCİ</t>
+          <t>TX IR-610 VHF VK VERİCİ</t>
         </is>
       </c>
       <c r="D232" s="3" t="n"/>
@@ -7297,13 +7600,13 @@
       <c r="H232" s="3" t="n"/>
       <c r="I232" s="3" t="n"/>
       <c r="J232" s="5" t="n">
-        <v>18214.93</v>
+        <v>11740.87</v>
       </c>
       <c r="K232" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L232" s="5" t="n">
-        <v>18214.93</v>
+        <v>11740.87</v>
       </c>
     </row>
     <row r="233" ht="18" customHeight="1">
@@ -7314,22 +7617,22 @@
       </c>
       <c r="B233" s="6" t="inlineStr">
         <is>
-          <t>MMVHF000011</t>
+          <t>MMVHF000001</t>
         </is>
       </c>
       <c r="C233" s="7" t="inlineStr">
         <is>
-          <t>TX IR-610 VHF CEPTE ANONSLU VERİCİ</t>
+          <t>TX IR-610 VHF VK VERİCİ</t>
         </is>
       </c>
       <c r="D233" s="6" t="inlineStr">
         <is>
-          <t>GMP-101-230124</t>
+          <t>GMP-101-230115</t>
         </is>
       </c>
       <c r="E233" s="7" t="inlineStr">
         <is>
-          <t>TX IR-610 VHF CEPTE ANONSLU VERİCİ</t>
+          <t>TX IR-610 VHF VK VERİCİ</t>
         </is>
       </c>
       <c r="F233" s="8" t="n">
@@ -7341,10 +7644,10 @@
         </is>
       </c>
       <c r="H233" s="9" t="n">
-        <v>18214.93</v>
+        <v>11740.8713</v>
       </c>
       <c r="I233" s="10" t="n">
-        <v>18214.93</v>
+        <v>11740.87</v>
       </c>
       <c r="J233" s="6" t="n"/>
       <c r="K233" s="6" t="n"/>
@@ -7358,12 +7661,12 @@
       </c>
       <c r="B234" s="11" t="inlineStr">
         <is>
-          <t>MMVHF000011</t>
+          <t>MMVHF000001</t>
         </is>
       </c>
       <c r="C234" s="12" t="inlineStr">
         <is>
-          <t>TX IR-610 VHF CEPTE ANONSLU VERİCİ</t>
+          <t>TX IR-610 VHF VK VERİCİ</t>
         </is>
       </c>
       <c r="D234" s="11" t="n"/>
@@ -7373,13 +7676,13 @@
       <c r="H234" s="11" t="n"/>
       <c r="I234" s="11" t="n"/>
       <c r="J234" s="13" t="n">
-        <v>18214.93</v>
+        <v>11740.87</v>
       </c>
       <c r="K234" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L234" s="13" t="n">
-        <v>18214.93</v>
+        <v>11740.87</v>
       </c>
     </row>
     <row r="235" ht="6" customHeight="1"/>
@@ -7391,12 +7694,12 @@
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>MMVRC000001</t>
+          <t>MMVHF000005</t>
         </is>
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>TX IR-610 5W VERİCİ GMP V1</t>
+          <t>TX IR-610 VHF CC EKRANLI VERİCİ</t>
         </is>
       </c>
       <c r="D236" s="3" t="n"/>
@@ -7423,22 +7726,22 @@
       </c>
       <c r="B237" s="6" t="inlineStr">
         <is>
-          <t>MMVRC000001</t>
+          <t>MMVHF000005</t>
         </is>
       </c>
       <c r="C237" s="7" t="inlineStr">
         <is>
-          <t>TX IR-610 5W VERİCİ GMP V1</t>
+          <t>TX IR-610 VHF CC EKRANLI VERİCİ</t>
         </is>
       </c>
       <c r="D237" s="6" t="inlineStr">
         <is>
-          <t>GMP-101-230125</t>
+          <t>GMP-101-230119</t>
         </is>
       </c>
       <c r="E237" s="7" t="inlineStr">
         <is>
-          <t>TX IR-610 5W VERİCİ GMP V1</t>
+          <t>TX IR-610 VHF CC EKRANLI VERİCİ</t>
         </is>
       </c>
       <c r="F237" s="8" t="n">
@@ -7467,12 +7770,12 @@
       </c>
       <c r="B238" s="11" t="inlineStr">
         <is>
-          <t>MMVRC000001</t>
+          <t>MMVHF000005</t>
         </is>
       </c>
       <c r="C238" s="12" t="inlineStr">
         <is>
-          <t>TX IR-610 5W VERİCİ GMP V1</t>
+          <t>TX IR-610 VHF CC EKRANLI VERİCİ</t>
         </is>
       </c>
       <c r="D238" s="11" t="n"/>
@@ -7500,12 +7803,12 @@
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>MMVRC000002</t>
+          <t>MMVHF000007</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>TX IR-610 5W LED DISPLAY VERİCİ GMP V2</t>
+          <t>TX IR-610 AVK VERİCİ TELSİZSİZ</t>
         </is>
       </c>
       <c r="D240" s="3" t="n"/>
@@ -7532,22 +7835,22 @@
       </c>
       <c r="B241" s="6" t="inlineStr">
         <is>
-          <t>MMVRC000002</t>
+          <t>MMVHF000007</t>
         </is>
       </c>
       <c r="C241" s="7" t="inlineStr">
         <is>
-          <t>TX IR-610 5W LED DISPLAY VERİCİ GMP V2</t>
+          <t>TX IR-610 AVK VERİCİ TELSİZSİZ</t>
         </is>
       </c>
       <c r="D241" s="6" t="inlineStr">
         <is>
-          <t>GMP-101-230126</t>
+          <t>GMP-101-230120</t>
         </is>
       </c>
       <c r="E241" s="7" t="inlineStr">
         <is>
-          <t>TX IR-610 5W LED DİSPLAY VERİCİ GMP V2</t>
+          <t>TX IR-610 AVK VERİCİ TELSİZSİZ</t>
         </is>
       </c>
       <c r="F241" s="8" t="n">
@@ -7576,12 +7879,12 @@
       </c>
       <c r="B242" s="11" t="inlineStr">
         <is>
-          <t>MMVRC000002</t>
+          <t>MMVHF000007</t>
         </is>
       </c>
       <c r="C242" s="12" t="inlineStr">
         <is>
-          <t>TX IR-610 5W LED DISPLAY VERİCİ GMP V2</t>
+          <t>TX IR-610 AVK VERİCİ TELSİZSİZ</t>
         </is>
       </c>
       <c r="D242" s="11" t="n"/>
@@ -7609,12 +7912,12 @@
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>MMVRC000003</t>
+          <t>MMVHF000008</t>
         </is>
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TX IR-610 GMP1 BAS KONUŞ </t>
+          <t>TX IR-610 VHF CC TON ATLAMALI VERİCİ</t>
         </is>
       </c>
       <c r="D244" s="3" t="n"/>
@@ -7641,22 +7944,22 @@
       </c>
       <c r="B245" s="6" t="inlineStr">
         <is>
-          <t>MMVRC000003</t>
+          <t>MMVHF000008</t>
         </is>
       </c>
       <c r="C245" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">TX IR-610 GMP1 BAS KONUŞ </t>
+          <t>TX IR-610 VHF CC TON ATLAMALI VERİCİ</t>
         </is>
       </c>
       <c r="D245" s="6" t="inlineStr">
         <is>
-          <t>GMP-101-230127</t>
+          <t>GMP-101-230121</t>
         </is>
       </c>
       <c r="E245" s="7" t="inlineStr">
         <is>
-          <t>TX IR-610 GMP 1 BAS KONUŞ</t>
+          <t xml:space="preserve">TX IR-610 VHF CC TON ATLAMALI VERİCİ </t>
         </is>
       </c>
       <c r="F245" s="8" t="n">
@@ -7685,12 +7988,12 @@
       </c>
       <c r="B246" s="11" t="inlineStr">
         <is>
-          <t>MMVRC000003</t>
+          <t>MMVHF000008</t>
         </is>
       </c>
       <c r="C246" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">TX IR-610 GMP1 BAS KONUŞ </t>
+          <t>TX IR-610 VHF CC TON ATLAMALI VERİCİ</t>
         </is>
       </c>
       <c r="D246" s="11" t="n"/>
@@ -7718,12 +8021,12 @@
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>MMVRC000004</t>
+          <t>MMVHF000011</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>TX IR-610 5W CC VERİCİ (BÜYÜK ŞASE)</t>
+          <t>TX IR-610 VHF CEPTE ANONSLU VERİCİ</t>
         </is>
       </c>
       <c r="D248" s="3" t="n"/>
@@ -7733,13 +8036,13 @@
       <c r="H248" s="3" t="n"/>
       <c r="I248" s="3" t="n"/>
       <c r="J248" s="5" t="n">
-        <v>0</v>
+        <v>18214.93</v>
       </c>
       <c r="K248" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L248" s="5" t="n">
-        <v>0</v>
+        <v>18214.93</v>
       </c>
     </row>
     <row r="249" ht="18" customHeight="1">
@@ -7750,23 +8053,22 @@
       </c>
       <c r="B249" s="6" t="inlineStr">
         <is>
-          <t>MMVRC000004</t>
+          <t>MMVHF000011</t>
         </is>
       </c>
       <c r="C249" s="7" t="inlineStr">
         <is>
-          <t>TX IR-610 5W CC VERİCİ (BÜYÜK ŞASE)</t>
+          <t>TX IR-610 VHF CEPTE ANONSLU VERİCİ</t>
         </is>
       </c>
       <c r="D249" s="6" t="inlineStr">
         <is>
-          <t>GMP-101-230128</t>
+          <t>GMP-101-230124</t>
         </is>
       </c>
       <c r="E249" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">TX IR-610 5W CC VERİCİ (BÜYÜK ŞASE)
-</t>
+          <t>TX IR-610 VHF CEPTE ANONSLU VERİCİ</t>
         </is>
       </c>
       <c r="F249" s="8" t="n">
@@ -7778,10 +8080,10 @@
         </is>
       </c>
       <c r="H249" s="9" t="n">
-        <v>0</v>
+        <v>18214.93</v>
       </c>
       <c r="I249" s="10" t="n">
-        <v>0</v>
+        <v>18214.93</v>
       </c>
       <c r="J249" s="6" t="n"/>
       <c r="K249" s="6" t="n"/>
@@ -7795,12 +8097,12 @@
       </c>
       <c r="B250" s="11" t="inlineStr">
         <is>
-          <t>MMVRC000004</t>
+          <t>MMVHF000011</t>
         </is>
       </c>
       <c r="C250" s="12" t="inlineStr">
         <is>
-          <t>TX IR-610 5W CC VERİCİ (BÜYÜK ŞASE)</t>
+          <t>TX IR-610 VHF CEPTE ANONSLU VERİCİ</t>
         </is>
       </c>
       <c r="D250" s="11" t="n"/>
@@ -7810,13 +8112,13 @@
       <c r="H250" s="11" t="n"/>
       <c r="I250" s="11" t="n"/>
       <c r="J250" s="13" t="n">
-        <v>0</v>
+        <v>18214.93</v>
       </c>
       <c r="K250" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L250" s="13" t="n">
-        <v>0</v>
+        <v>18214.93</v>
       </c>
     </row>
     <row r="251" ht="6" customHeight="1"/>
@@ -7828,12 +8130,12 @@
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>YMB-V00R00-220007</t>
+          <t>MMVRC000001</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>LED BÜTÜNÜ</t>
+          <t>TX IR-610 5W VERİCİ GMP V1</t>
         </is>
       </c>
       <c r="D252" s="3" t="n"/>
@@ -7843,13 +8145,13 @@
       <c r="H252" s="3" t="n"/>
       <c r="I252" s="3" t="n"/>
       <c r="J252" s="5" t="n">
-        <v>199.74</v>
+        <v>0</v>
       </c>
       <c r="K252" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L252" s="5" t="n">
-        <v>199.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253" ht="18" customHeight="1">
@@ -7860,23 +8162,22 @@
       </c>
       <c r="B253" s="6" t="inlineStr">
         <is>
-          <t>YMB-V00R00-220007</t>
+          <t>MMVRC000001</t>
         </is>
       </c>
       <c r="C253" s="7" t="inlineStr">
         <is>
-          <t>LED BÜTÜNÜ</t>
+          <t>TX IR-610 5W VERİCİ GMP V1</t>
         </is>
       </c>
       <c r="D253" s="6" t="inlineStr">
         <is>
-          <t>GMP-300-230004</t>
+          <t>GMP-101-230125</t>
         </is>
       </c>
       <c r="E253" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORTATİF DİZGİ POKO PİN KART (Seri Üretim) 
-</t>
+          <t>TX IR-610 5W VERİCİ GMP V1</t>
         </is>
       </c>
       <c r="F253" s="8" t="n">
@@ -7888,93 +8189,531 @@
         </is>
       </c>
       <c r="H253" s="9" t="n">
-        <v>199.74</v>
+        <v>0</v>
       </c>
       <c r="I253" s="10" t="n">
-        <v>199.74</v>
+        <v>0</v>
       </c>
       <c r="J253" s="6" t="n"/>
       <c r="K253" s="6" t="n"/>
       <c r="L253" s="6" t="n"/>
     </row>
-    <row r="254" ht="18" customHeight="1">
-      <c r="A254" s="6" t="inlineStr">
-        <is>
-          <t>BİLEŞEN</t>
-        </is>
-      </c>
-      <c r="B254" s="6" t="inlineStr">
+    <row r="254" ht="20" customHeight="1">
+      <c r="A254" s="11" t="inlineStr">
+        <is>
+          <t>TOPLAM</t>
+        </is>
+      </c>
+      <c r="B254" s="11" t="inlineStr">
+        <is>
+          <t>MMVRC000001</t>
+        </is>
+      </c>
+      <c r="C254" s="12" t="inlineStr">
+        <is>
+          <t>TX IR-610 5W VERİCİ GMP V1</t>
+        </is>
+      </c>
+      <c r="D254" s="11" t="n"/>
+      <c r="E254" s="11" t="n"/>
+      <c r="F254" s="11" t="n"/>
+      <c r="G254" s="11" t="n"/>
+      <c r="H254" s="11" t="n"/>
+      <c r="I254" s="11" t="n"/>
+      <c r="J254" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K254" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L254" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" ht="6" customHeight="1"/>
+    <row r="256" ht="22" customHeight="1">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>MAMÜL</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>MMVRC000002</t>
+        </is>
+      </c>
+      <c r="C256" s="4" t="inlineStr">
+        <is>
+          <t>TX IR-610 5W LED DISPLAY VERİCİ GMP V2</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="n"/>
+      <c r="E256" s="3" t="n"/>
+      <c r="F256" s="3" t="n"/>
+      <c r="G256" s="3" t="n"/>
+      <c r="H256" s="3" t="n"/>
+      <c r="I256" s="3" t="n"/>
+      <c r="J256" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K256" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L256" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" ht="18" customHeight="1">
+      <c r="A257" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B257" s="6" t="inlineStr">
+        <is>
+          <t>MMVRC000002</t>
+        </is>
+      </c>
+      <c r="C257" s="7" t="inlineStr">
+        <is>
+          <t>TX IR-610 5W LED DISPLAY VERİCİ GMP V2</t>
+        </is>
+      </c>
+      <c r="D257" s="6" t="inlineStr">
+        <is>
+          <t>GMP-101-230126</t>
+        </is>
+      </c>
+      <c r="E257" s="7" t="inlineStr">
+        <is>
+          <t>TX IR-610 5W LED DİSPLAY VERİCİ GMP V2</t>
+        </is>
+      </c>
+      <c r="F257" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G257" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H257" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I257" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J257" s="6" t="n"/>
+      <c r="K257" s="6" t="n"/>
+      <c r="L257" s="6" t="n"/>
+    </row>
+    <row r="258" ht="20" customHeight="1">
+      <c r="A258" s="11" t="inlineStr">
+        <is>
+          <t>TOPLAM</t>
+        </is>
+      </c>
+      <c r="B258" s="11" t="inlineStr">
+        <is>
+          <t>MMVRC000002</t>
+        </is>
+      </c>
+      <c r="C258" s="12" t="inlineStr">
+        <is>
+          <t>TX IR-610 5W LED DISPLAY VERİCİ GMP V2</t>
+        </is>
+      </c>
+      <c r="D258" s="11" t="n"/>
+      <c r="E258" s="11" t="n"/>
+      <c r="F258" s="11" t="n"/>
+      <c r="G258" s="11" t="n"/>
+      <c r="H258" s="11" t="n"/>
+      <c r="I258" s="11" t="n"/>
+      <c r="J258" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K258" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L258" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" ht="6" customHeight="1"/>
+    <row r="260" ht="22" customHeight="1">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>MAMÜL</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>MMVRC000003</t>
+        </is>
+      </c>
+      <c r="C260" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TX IR-610 GMP1 BAS KONUŞ </t>
+        </is>
+      </c>
+      <c r="D260" s="3" t="n"/>
+      <c r="E260" s="3" t="n"/>
+      <c r="F260" s="3" t="n"/>
+      <c r="G260" s="3" t="n"/>
+      <c r="H260" s="3" t="n"/>
+      <c r="I260" s="3" t="n"/>
+      <c r="J260" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K260" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L260" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" ht="18" customHeight="1">
+      <c r="A261" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B261" s="6" t="inlineStr">
+        <is>
+          <t>MMVRC000003</t>
+        </is>
+      </c>
+      <c r="C261" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TX IR-610 GMP1 BAS KONUŞ </t>
+        </is>
+      </c>
+      <c r="D261" s="6" t="inlineStr">
+        <is>
+          <t>GMP-101-230127</t>
+        </is>
+      </c>
+      <c r="E261" s="7" t="inlineStr">
+        <is>
+          <t>TX IR-610 GMP 1 BAS KONUŞ</t>
+        </is>
+      </c>
+      <c r="F261" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G261" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H261" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I261" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J261" s="6" t="n"/>
+      <c r="K261" s="6" t="n"/>
+      <c r="L261" s="6" t="n"/>
+    </row>
+    <row r="262" ht="20" customHeight="1">
+      <c r="A262" s="11" t="inlineStr">
+        <is>
+          <t>TOPLAM</t>
+        </is>
+      </c>
+      <c r="B262" s="11" t="inlineStr">
+        <is>
+          <t>MMVRC000003</t>
+        </is>
+      </c>
+      <c r="C262" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TX IR-610 GMP1 BAS KONUŞ </t>
+        </is>
+      </c>
+      <c r="D262" s="11" t="n"/>
+      <c r="E262" s="11" t="n"/>
+      <c r="F262" s="11" t="n"/>
+      <c r="G262" s="11" t="n"/>
+      <c r="H262" s="11" t="n"/>
+      <c r="I262" s="11" t="n"/>
+      <c r="J262" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K262" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L262" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" ht="6" customHeight="1"/>
+    <row r="264" ht="22" customHeight="1">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>MAMÜL</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>MMVRC000004</t>
+        </is>
+      </c>
+      <c r="C264" s="4" t="inlineStr">
+        <is>
+          <t>TX IR-610 5W CC VERİCİ (BÜYÜK ŞASE)</t>
+        </is>
+      </c>
+      <c r="D264" s="3" t="n"/>
+      <c r="E264" s="3" t="n"/>
+      <c r="F264" s="3" t="n"/>
+      <c r="G264" s="3" t="n"/>
+      <c r="H264" s="3" t="n"/>
+      <c r="I264" s="3" t="n"/>
+      <c r="J264" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K264" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L264" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" ht="18" customHeight="1">
+      <c r="A265" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B265" s="6" t="inlineStr">
+        <is>
+          <t>MMVRC000004</t>
+        </is>
+      </c>
+      <c r="C265" s="7" t="inlineStr">
+        <is>
+          <t>TX IR-610 5W CC VERİCİ (BÜYÜK ŞASE)</t>
+        </is>
+      </c>
+      <c r="D265" s="6" t="inlineStr">
+        <is>
+          <t>GMP-101-230128</t>
+        </is>
+      </c>
+      <c r="E265" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TX IR-610 5W CC VERİCİ (BÜYÜK ŞASE)
+</t>
+        </is>
+      </c>
+      <c r="F265" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G265" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H265" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I265" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J265" s="6" t="n"/>
+      <c r="K265" s="6" t="n"/>
+      <c r="L265" s="6" t="n"/>
+    </row>
+    <row r="266" ht="20" customHeight="1">
+      <c r="A266" s="11" t="inlineStr">
+        <is>
+          <t>TOPLAM</t>
+        </is>
+      </c>
+      <c r="B266" s="11" t="inlineStr">
+        <is>
+          <t>MMVRC000004</t>
+        </is>
+      </c>
+      <c r="C266" s="12" t="inlineStr">
+        <is>
+          <t>TX IR-610 5W CC VERİCİ (BÜYÜK ŞASE)</t>
+        </is>
+      </c>
+      <c r="D266" s="11" t="n"/>
+      <c r="E266" s="11" t="n"/>
+      <c r="F266" s="11" t="n"/>
+      <c r="G266" s="11" t="n"/>
+      <c r="H266" s="11" t="n"/>
+      <c r="I266" s="11" t="n"/>
+      <c r="J266" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K266" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L266" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" ht="6" customHeight="1"/>
+    <row r="268" ht="22" customHeight="1">
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t>MAMÜL</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
         <is>
           <t>YMB-V00R00-220007</t>
         </is>
       </c>
-      <c r="C254" s="7" t="inlineStr">
+      <c r="C268" s="4" t="inlineStr">
         <is>
           <t>LED BÜTÜNÜ</t>
         </is>
       </c>
-      <c r="D254" s="6" t="inlineStr">
+      <c r="D268" s="3" t="n"/>
+      <c r="E268" s="3" t="n"/>
+      <c r="F268" s="3" t="n"/>
+      <c r="G268" s="3" t="n"/>
+      <c r="H268" s="3" t="n"/>
+      <c r="I268" s="3" t="n"/>
+      <c r="J268" s="5" t="n">
+        <v>199.74</v>
+      </c>
+      <c r="K268" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L268" s="5" t="n">
+        <v>199.74</v>
+      </c>
+    </row>
+    <row r="269" ht="18" customHeight="1">
+      <c r="A269" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B269" s="6" t="inlineStr">
+        <is>
+          <t>YMB-V00R00-220007</t>
+        </is>
+      </c>
+      <c r="C269" s="7" t="inlineStr">
+        <is>
+          <t>LED BÜTÜNÜ</t>
+        </is>
+      </c>
+      <c r="D269" s="6" t="inlineStr">
+        <is>
+          <t>GMP-300-230004</t>
+        </is>
+      </c>
+      <c r="E269" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PORTATİF DİZGİ POKO PİN KART (Seri Üretim) 
+</t>
+        </is>
+      </c>
+      <c r="F269" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G269" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H269" s="9" t="n">
+        <v>199.74</v>
+      </c>
+      <c r="I269" s="10" t="n">
+        <v>199.74</v>
+      </c>
+      <c r="J269" s="6" t="n"/>
+      <c r="K269" s="6" t="n"/>
+      <c r="L269" s="6" t="n"/>
+    </row>
+    <row r="270" ht="18" customHeight="1">
+      <c r="A270" s="6" t="inlineStr">
+        <is>
+          <t>BİLEŞEN</t>
+        </is>
+      </c>
+      <c r="B270" s="6" t="inlineStr">
+        <is>
+          <t>YMB-V00R00-220007</t>
+        </is>
+      </c>
+      <c r="C270" s="7" t="inlineStr">
+        <is>
+          <t>LED BÜTÜNÜ</t>
+        </is>
+      </c>
+      <c r="D270" s="6" t="inlineStr">
         <is>
           <t>GMP-300-230005</t>
         </is>
       </c>
-      <c r="E254" s="7" t="inlineStr">
+      <c r="E270" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">PORTATİF DİZGİ LED KART (SERİ ÜRETİM)
 </t>
         </is>
       </c>
-      <c r="F254" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G254" s="6" t="inlineStr">
-        <is>
-          <t>ADET</t>
-        </is>
-      </c>
-      <c r="H254" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I254" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J254" s="6" t="n"/>
-      <c r="K254" s="6" t="n"/>
-      <c r="L254" s="6" t="n"/>
-    </row>
-    <row r="255" ht="20" customHeight="1">
-      <c r="A255" s="11" t="inlineStr">
+      <c r="F270" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G270" s="6" t="inlineStr">
+        <is>
+          <t>ADET</t>
+        </is>
+      </c>
+      <c r="H270" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I270" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J270" s="6" t="n"/>
+      <c r="K270" s="6" t="n"/>
+      <c r="L270" s="6" t="n"/>
+    </row>
+    <row r="271" ht="20" customHeight="1">
+      <c r="A271" s="11" t="inlineStr">
         <is>
           <t>TOPLAM</t>
         </is>
       </c>
-      <c r="B255" s="11" t="inlineStr">
+      <c r="B271" s="11" t="inlineStr">
         <is>
           <t>YMB-V00R00-220007</t>
         </is>
       </c>
-      <c r="C255" s="12" t="inlineStr">
+      <c r="C271" s="12" t="inlineStr">
         <is>
           <t>LED BÜTÜNÜ</t>
         </is>
       </c>
-      <c r="D255" s="11" t="n"/>
-      <c r="E255" s="11" t="n"/>
-      <c r="F255" s="11" t="n"/>
-      <c r="G255" s="11" t="n"/>
-      <c r="H255" s="11" t="n"/>
-      <c r="I255" s="11" t="n"/>
-      <c r="J255" s="13" t="n">
+      <c r="D271" s="11" t="n"/>
+      <c r="E271" s="11" t="n"/>
+      <c r="F271" s="11" t="n"/>
+      <c r="G271" s="11" t="n"/>
+      <c r="H271" s="11" t="n"/>
+      <c r="I271" s="11" t="n"/>
+      <c r="J271" s="13" t="n">
         <v>199.74</v>
       </c>
-      <c r="K255" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L255" s="13" t="n">
+      <c r="K271" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L271" s="13" t="n">
         <v>199.74</v>
       </c>
     </row>
-    <row r="256" ht="6" customHeight="1"/>
+    <row r="272" ht="6" customHeight="1"/>
   </sheetData>
   <autoFilter ref="A2:L2"/>
   <mergeCells count="1">
